--- a/Car_Wash_Advisory_Companies.xlsx
+++ b/Car_Wash_Advisory_Companies.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="581">
   <si>
     <t>Company Name</t>
   </si>
@@ -94,7 +94,7 @@
     <t>Golden Gate Capital</t>
   </si>
   <si>
-    <t>Alabama | Arkansas | Florida | Georgia | Idaho | Illinois | Indiana | Iowa | Kansas | Kentucky | Michigan | Minnesota | Mississippi | Missouri | Montana | Nebraska | New Mexico | New York | North Carolina | North Dakota | Tennessee | Texas | Virginia | West Virginia | Wisconsin</t>
+    <t>Alabama | Arkansas | Florida | Georgia | Idaho | Illinois | Indiana | Iowa | Kansas | Kentucky | Michigan | Minnesota | Mississippi | Missouri | Montana | Nebraska | New Mexico | New York | North Carolina | North Dakota | Ohio | Oklahoma | Pennsylvania | South Carolina | South Dakota | Tennessee | Virginia | West Virginia | Wisconsin | Texas</t>
   </si>
   <si>
     <t>https://www.tidalwaveautospa.com/</t>
@@ -325,6 +325,12 @@
     <t>https://luvcarwash.com/</t>
   </si>
   <si>
+    <t>Splash Car Wash &amp; Oil Change</t>
+  </si>
+  <si>
+    <t>https://cleancarfast.com</t>
+  </si>
+  <si>
     <t>Splash Car Wash</t>
   </si>
   <si>
@@ -352,6 +358,18 @@
     <t>https://truebluecw.com/</t>
   </si>
   <si>
+    <t>Crew Carwash</t>
+  </si>
+  <si>
+    <t>Indiana</t>
+  </si>
+  <si>
+    <t>Indiana | Minnesota</t>
+  </si>
+  <si>
+    <t>https://crewcarwash.com/</t>
+  </si>
+  <si>
     <t>Splash in ECO Car Wash</t>
   </si>
   <si>
@@ -412,18 +430,6 @@
     <t>https://www.bigdanscarwash.com/</t>
   </si>
   <si>
-    <t>Crew Carwash</t>
-  </si>
-  <si>
-    <t>Indiana</t>
-  </si>
-  <si>
-    <t>Indiana | Minnesota</t>
-  </si>
-  <si>
-    <t>https://crewcarwash.com/</t>
-  </si>
-  <si>
     <t>Auto Wash Car Wash</t>
   </si>
   <si>
@@ -478,6 +484,18 @@
     <t>https://www.mywashnroll.com/</t>
   </si>
   <si>
+    <t>Rich's Car Wash</t>
+  </si>
+  <si>
+    <t>Alabama</t>
+  </si>
+  <si>
+    <t>Alabama | Florida | Georgia | Louisiana | Mississippi | Texas</t>
+  </si>
+  <si>
+    <t>https://www.richscarwash.com/</t>
+  </si>
+  <si>
     <t>Terrible Herbst</t>
   </si>
   <si>
@@ -523,18 +541,6 @@
     <t>https://www.sparklingimage.com/</t>
   </si>
   <si>
-    <t>Rich's Car Wash</t>
-  </si>
-  <si>
-    <t>Alabama</t>
-  </si>
-  <si>
-    <t>Alabama | Florida | Georgia | Louisiana | Mississippi | Texas</t>
-  </si>
-  <si>
-    <t>https://www.richscarwash.com/</t>
-  </si>
-  <si>
     <t>Surf Thru Express Car Wash</t>
   </si>
   <si>
@@ -562,6 +568,81 @@
     <t>https://www.gasnwash.net/</t>
   </si>
   <si>
+    <t>Hoffman Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.hoffmancarwash.com/</t>
+  </si>
+  <si>
+    <t>Delta Sonic</t>
+  </si>
+  <si>
+    <t>New York | Illinois | Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://www.deltasoniccarwash.com/</t>
+  </si>
+  <si>
+    <t>Tagg-N-Go</t>
+  </si>
+  <si>
+    <t>Utah</t>
+  </si>
+  <si>
+    <t>Utah | Nevada | Idaho</t>
+  </si>
+  <si>
+    <t>https://taggngo.com/</t>
+  </si>
+  <si>
+    <t>Glide XPRESS Car Wash</t>
+  </si>
+  <si>
+    <t>Tennessee | Missouri | Arkansas | Mississippi</t>
+  </si>
+  <si>
+    <t>https://www.glidexwash.com/</t>
+  </si>
+  <si>
+    <t>Flash Car Wash</t>
+  </si>
+  <si>
+    <t>Connecticut | Massachusetts | Rhode Island</t>
+  </si>
+  <si>
+    <t>https://flashcarwashes.com/</t>
+  </si>
+  <si>
+    <t>Hurricane Express Wash</t>
+  </si>
+  <si>
+    <t>South Carolina</t>
+  </si>
+  <si>
+    <t>PassiveInvesting.com</t>
+  </si>
+  <si>
+    <t>Tennessee | South Carolina | North Carolina | Florida | Maryland | Virginia | Alabama</t>
+  </si>
+  <si>
+    <t>https://www.hurricanewash.com/</t>
+  </si>
+  <si>
+    <t>Soapy Joe’s Car Wash</t>
+  </si>
+  <si>
+    <t>https://soapyjoescarwash.com/</t>
+  </si>
+  <si>
+    <t>Waterway Carwash</t>
+  </si>
+  <si>
+    <t>Kansas | Montana | Colorado | Illinois | Ohio</t>
+  </si>
+  <si>
+    <t>https://www.waterway.com/</t>
+  </si>
+  <si>
     <t>Mighty Wash</t>
   </si>
   <si>
@@ -571,34 +652,97 @@
     <t>https://mymightywash.com/</t>
   </si>
   <si>
-    <t>Delta Sonic</t>
-  </si>
-  <si>
-    <t>New York | Illinois | Pennsylvania</t>
-  </si>
-  <si>
-    <t>https://www.deltasoniccarwash.com/</t>
-  </si>
-  <si>
-    <t>Tagg-N-Go</t>
-  </si>
-  <si>
-    <t>Utah</t>
-  </si>
-  <si>
-    <t>Utah | Nevada | Idaho</t>
-  </si>
-  <si>
-    <t>https://taggngo.com/</t>
-  </si>
-  <si>
-    <t>Glide XPRESS Car Wash</t>
-  </si>
-  <si>
-    <t>Tennessee | Missouri | Arkansas | Mississippi</t>
-  </si>
-  <si>
-    <t>https://www.glidexwash.com/</t>
+    <t>Trademark Car Wash</t>
+  </si>
+  <si>
+    <t>Princeton Equity Group / Accelerated Brands</t>
+  </si>
+  <si>
+    <t>Texas | Louisiana | Florida | New Mexico | Arizona | Tennessee | Michigan | Missouri</t>
+  </si>
+  <si>
+    <t>https://trademarkcarwash.com/</t>
+  </si>
+  <si>
+    <t>Quick N Clean</t>
+  </si>
+  <si>
+    <t>Arizona | Colorado | Oklahoma | Texas</t>
+  </si>
+  <si>
+    <t>https://quicknclean.net/</t>
+  </si>
+  <si>
+    <t>Ronny's Car Wash</t>
+  </si>
+  <si>
+    <t>Florida | Alabama</t>
+  </si>
+  <si>
+    <t>https://ronnyscarwash.net/</t>
+  </si>
+  <si>
+    <t>Sud Stop Car Wash</t>
+  </si>
+  <si>
+    <t>Real Capital Partners</t>
+  </si>
+  <si>
+    <t>Florida | Georgia | Alabama | North Carolina | South Carolina</t>
+  </si>
+  <si>
+    <t>https://www.sudstopcarwash.com/</t>
+  </si>
+  <si>
+    <t>Thoroughbred Express Auto Wash</t>
+  </si>
+  <si>
+    <t>Kentucky</t>
+  </si>
+  <si>
+    <t>Freestone Capital</t>
+  </si>
+  <si>
+    <t>Indiana | Kentucky | Ohio | Oregon | West Virginia | Washington</t>
+  </si>
+  <si>
+    <t>https://thoroughbredexpress.com/</t>
+  </si>
+  <si>
+    <t>Flagstop Car Wash</t>
+  </si>
+  <si>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>Garnet Station Partners</t>
+  </si>
+  <si>
+    <t>https://www.flagstopcarwash.com/</t>
+  </si>
+  <si>
+    <t>Rocket Carwash</t>
+  </si>
+  <si>
+    <t>Nebraska</t>
+  </si>
+  <si>
+    <t>City+Ventures</t>
+  </si>
+  <si>
+    <t>Nebraska | Pennsylvania | Texas | California | Iowa | Utah | Florida</t>
+  </si>
+  <si>
+    <t>https://rocketcarwash.com/</t>
+  </si>
+  <si>
+    <t>Wash Masters Car Wash</t>
+  </si>
+  <si>
+    <t>Victron Energy Company</t>
+  </si>
+  <si>
+    <t>https://washmasters.com/</t>
   </si>
   <si>
     <t>Washville Car Wash</t>
@@ -613,205 +757,91 @@
     <t>https://washvillecarwash.com/</t>
   </si>
   <si>
-    <t>Flash Car Wash</t>
-  </si>
-  <si>
-    <t>Connecticut | Massachusetts | Rhode Island</t>
-  </si>
-  <si>
-    <t>https://flashcarwashes.com/</t>
-  </si>
-  <si>
-    <t>Hurricane Express Wash</t>
-  </si>
-  <si>
-    <t>South Carolina</t>
-  </si>
-  <si>
-    <t>PassiveInvesting.com</t>
-  </si>
-  <si>
-    <t>Tennessee | South Carolina | North Carolina | Florida | Maryland | Virginia | Alabama</t>
-  </si>
-  <si>
-    <t>https://www.hurricanewash.com/</t>
-  </si>
-  <si>
-    <t>Soapy Joe’s Car Wash</t>
-  </si>
-  <si>
-    <t>https://soapyjoescarwash.com/</t>
-  </si>
-  <si>
-    <t>Waterway Carwash</t>
-  </si>
-  <si>
-    <t>Kansas | Montana | Colorado | Illinois | Ohio</t>
-  </si>
-  <si>
-    <t>https://www.waterway.com/</t>
-  </si>
-  <si>
-    <t>Hoffman Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.hoffmancarwash.com/</t>
-  </si>
-  <si>
-    <t>Trademark Car Wash</t>
-  </si>
-  <si>
-    <t>Princeton Equity Group / Accelerated Brands</t>
-  </si>
-  <si>
-    <t>Texas | Louisiana | Florida | New Mexico | Arizona | Tennessee | Michigan | Missouri</t>
-  </si>
-  <si>
-    <t>https://trademarkcarwash.com/</t>
-  </si>
-  <si>
-    <t>Quick N Clean</t>
-  </si>
-  <si>
-    <t>Arizona | Colorado | Oklahoma | Texas</t>
-  </si>
-  <si>
-    <t>https://quicknclean.net/</t>
-  </si>
-  <si>
-    <t>Ronny's Car Wash</t>
-  </si>
-  <si>
-    <t>Florida | Alabama</t>
-  </si>
-  <si>
-    <t>https://ronnyscarwash.net/</t>
-  </si>
-  <si>
-    <t>Sud Stop Car Wash</t>
-  </si>
-  <si>
-    <t>Real Capital Partners</t>
-  </si>
-  <si>
-    <t>Florida | Georgia | Alabama | North Carolina | South Carolina</t>
-  </si>
-  <si>
-    <t>https://www.sudstopcarwash.com/</t>
-  </si>
-  <si>
-    <t>Thoroughbred Express Auto Wash</t>
-  </si>
-  <si>
-    <t>Kentucky</t>
-  </si>
-  <si>
-    <t>Freestone Capital</t>
-  </si>
-  <si>
-    <t>Indiana | Kentucky | Ohio | Oregon | West Virginia | Washington</t>
-  </si>
-  <si>
-    <t>https://thoroughbredexpress.com/</t>
-  </si>
-  <si>
-    <t>Flagstop Car Wash</t>
-  </si>
-  <si>
-    <t>Virginia</t>
-  </si>
-  <si>
-    <t>Garnet Station Partners</t>
-  </si>
-  <si>
-    <t>https://www.flagstopcarwash.com/</t>
-  </si>
-  <si>
-    <t>Rocket Carwash</t>
-  </si>
-  <si>
-    <t>Nebraska</t>
-  </si>
-  <si>
-    <t>City+Ventures</t>
-  </si>
-  <si>
-    <t>Nebraska | Pennsylvania | Texas | California | Iowa | Utah | Florida</t>
-  </si>
-  <si>
-    <t>https://rocketcarwash.com/</t>
-  </si>
-  <si>
-    <t>Wash Masters Car Wash</t>
-  </si>
-  <si>
-    <t>Victron Energy Company</t>
-  </si>
-  <si>
-    <t>https://washmasters.com/</t>
-  </si>
-  <si>
     <t>Dash Car Wash</t>
   </si>
   <si>
     <t>Arizona | Nevada</t>
   </si>
   <si>
+    <t>Mr. Magic Car Wash</t>
+  </si>
+  <si>
+    <t>Pennsylvania</t>
+  </si>
+  <si>
+    <t>Incline Equity Partners</t>
+  </si>
+  <si>
+    <t>Pennsylvania | West Virginia | Ohio</t>
+  </si>
+  <si>
+    <t>https://mrmagiccarwash.com/</t>
+  </si>
+  <si>
+    <t>Shiny Shell Car Wash</t>
+  </si>
+  <si>
+    <t>Utah | Pennsylvania | Maryland</t>
+  </si>
+  <si>
+    <t>https://www.shinyshell.com/</t>
+  </si>
+  <si>
+    <t>The Wash Tub</t>
+  </si>
+  <si>
+    <t>https://www.washtub.com/</t>
+  </si>
+  <si>
+    <t>Carnation Auto Spa</t>
+  </si>
+  <si>
+    <t>Iron Skillet Partners</t>
+  </si>
+  <si>
+    <t>https://carnationautospa.com/</t>
+  </si>
+  <si>
+    <t>Dirty Dog’s Car Wash</t>
+  </si>
+  <si>
+    <t>Cynosure Group</t>
+  </si>
+  <si>
+    <t>Alabama | Florida | Georgia</t>
+  </si>
+  <si>
+    <t>https://dirtydogscarwash.com/</t>
+  </si>
+  <si>
+    <t>ScrubaDub Auto Wash Centers</t>
+  </si>
+  <si>
+    <t>Massachusetts | Rhode Island | Maine | New Hampshire</t>
+  </si>
+  <si>
+    <t>https://www.scrubadub.com/</t>
+  </si>
+  <si>
+    <t>Team Car Wash</t>
+  </si>
+  <si>
+    <t>New Jersey</t>
+  </si>
+  <si>
+    <t>https://theteamcarwash.com/</t>
+  </si>
+  <si>
     <t>Fast 5 Xpress Car Wash</t>
   </si>
   <si>
     <t>https://www.fast5xpress.com/</t>
   </si>
   <si>
-    <t>Mr. Magic Car Wash</t>
-  </si>
-  <si>
-    <t>Pennsylvania</t>
-  </si>
-  <si>
-    <t>Incline Equity Partners</t>
-  </si>
-  <si>
-    <t>Pennsylvania | West Virginia | Ohio</t>
-  </si>
-  <si>
-    <t>https://mrmagiccarwash.com/</t>
-  </si>
-  <si>
-    <t>Shiny Shell Car Wash</t>
-  </si>
-  <si>
-    <t>Utah | Pennsylvania | Maryland</t>
-  </si>
-  <si>
-    <t>https://www.shinyshell.com/</t>
-  </si>
-  <si>
-    <t>The Wash Tub</t>
-  </si>
-  <si>
-    <t>https://www.washtub.com/</t>
-  </si>
-  <si>
-    <t>Carnation Auto Spa</t>
-  </si>
-  <si>
-    <t>Iron Skillet Partners</t>
-  </si>
-  <si>
-    <t>https://carnationautospa.com/</t>
-  </si>
-  <si>
-    <t>Dirty Dog’s Car Wash</t>
-  </si>
-  <si>
-    <t>Cynosure Group</t>
-  </si>
-  <si>
-    <t>Alabama | Florida | Georgia</t>
-  </si>
-  <si>
-    <t>https://dirtydogscarwash.com/</t>
+    <t>Buddy Bear Car Wash</t>
+  </si>
+  <si>
+    <t>https://buddybearcarwash.com/</t>
   </si>
   <si>
     <t>Elephant Super Car Wash</t>
@@ -823,13 +853,190 @@
     <t>https://elephantcarwash.com/</t>
   </si>
   <si>
-    <t>ScrubaDub Auto Wash Centers</t>
-  </si>
-  <si>
-    <t>Massachusetts | Rhode Island | Maine | New Hampshire</t>
-  </si>
-  <si>
-    <t>https://www.scrubadub.com/</t>
+    <t>Drive &amp; Shine Car Wash</t>
+  </si>
+  <si>
+    <t>Indiana | Michigan</t>
+  </si>
+  <si>
+    <t>https://driveandshine.com/</t>
+  </si>
+  <si>
+    <t>Gate Express Car Wash</t>
+  </si>
+  <si>
+    <t>https://gateexpresscarwash.com/</t>
+  </si>
+  <si>
+    <t>TruShine Car Wash</t>
+  </si>
+  <si>
+    <t>Tennessee | Virginia</t>
+  </si>
+  <si>
+    <t>https://www.trushinecarwash.com/</t>
+  </si>
+  <si>
+    <t>WOW Carwash</t>
+  </si>
+  <si>
+    <t>Garnett Station Partners, LLC</t>
+  </si>
+  <si>
+    <t>https://wowwash.com/</t>
+  </si>
+  <si>
+    <t>Big Peach Car Wash</t>
+  </si>
+  <si>
+    <t>Georgia | Tennessee | Florida</t>
+  </si>
+  <si>
+    <t>Francis &amp; Sons Car Wash</t>
+  </si>
+  <si>
+    <t>Acquired by Raceway Car Wash</t>
+  </si>
+  <si>
+    <t>https://francisandsonscarwash.com/</t>
+  </si>
+  <si>
+    <t>Blue Tide Car Wash</t>
+  </si>
+  <si>
+    <t>South Dakota</t>
+  </si>
+  <si>
+    <t>https://bluetidecarwash.com/</t>
+  </si>
+  <si>
+    <t>Fuller's Car Wash</t>
+  </si>
+  <si>
+    <t>https://fullerscarwash.com/</t>
+  </si>
+  <si>
+    <t>Kaady Car Wash</t>
+  </si>
+  <si>
+    <t>Oregon | Washington | California</t>
+  </si>
+  <si>
+    <t>https://kaady.com/</t>
+  </si>
+  <si>
+    <t>Washman Car Washes</t>
+  </si>
+  <si>
+    <t>https://www.washmanusa.com/</t>
+  </si>
+  <si>
+    <t>Bliss Car Wash</t>
+  </si>
+  <si>
+    <t>https://blisscarwash.com/</t>
+  </si>
+  <si>
+    <t>Cheetah Clean Auto Wash</t>
+  </si>
+  <si>
+    <t>Kentucky | Tennessee</t>
+  </si>
+  <si>
+    <t>https://cheetahclean.com/</t>
+  </si>
+  <si>
+    <t>Fast Eddie's Car Wash &amp; Oil Change</t>
+  </si>
+  <si>
+    <t>https://www.fasteddiescarcare.com/</t>
+  </si>
+  <si>
+    <t>Raindrop Car Wash</t>
+  </si>
+  <si>
+    <t>https://raindropcarwash.com/</t>
+  </si>
+  <si>
+    <t>Rainforest Carwash &amp; Oil Change</t>
+  </si>
+  <si>
+    <t>Louisiana</t>
+  </si>
+  <si>
+    <t>Louisiana | Mississippi</t>
+  </si>
+  <si>
+    <t>https://rainforestclean.com/</t>
+  </si>
+  <si>
+    <t>Zax Auto Wash</t>
+  </si>
+  <si>
+    <t>https://zaxautowash.com/</t>
+  </si>
+  <si>
+    <t>Breeze Thru Car Wash</t>
+  </si>
+  <si>
+    <t>Colorado | Wyoming</t>
+  </si>
+  <si>
+    <t>https://breezethrucarwash.com/</t>
+  </si>
+  <si>
+    <t>Car Spa</t>
+  </si>
+  <si>
+    <t>Florida | Georgia | Texas | Virginia</t>
+  </si>
+  <si>
+    <t>https://carspa.net/</t>
+  </si>
+  <si>
+    <t>Haffner's</t>
+  </si>
+  <si>
+    <t>Massachusetts | New Hampshire</t>
+  </si>
+  <si>
+    <t>https://haffners.com/</t>
+  </si>
+  <si>
+    <t>Mr. Sparkle Car Wash</t>
+  </si>
+  <si>
+    <t>Connecticut | Massachusetts | New Jersey</t>
+  </si>
+  <si>
+    <t>https://www.mrsparklecarwash.com/</t>
+  </si>
+  <si>
+    <t>Rocky Mountain Car Wash</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>Wyoming | Montana</t>
+  </si>
+  <si>
+    <t>https://rockymountaincarwash.com/</t>
+  </si>
+  <si>
+    <t>Sgt. Clean Car Wash</t>
+  </si>
+  <si>
+    <t>https://sgtclean.com/</t>
+  </si>
+  <si>
+    <t>Shammy Shine Car Washes</t>
+  </si>
+  <si>
+    <t>New Jersey | Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://www.shammyshine.com/</t>
   </si>
   <si>
     <t>Suds Deluxe Car Wash</t>
@@ -838,201 +1045,6 @@
     <t>https://www.sudsdeluxe.com/</t>
   </si>
   <si>
-    <t>Splash Car Wash &amp; Oil Change</t>
-  </si>
-  <si>
-    <t>https://cleancarfast.com</t>
-  </si>
-  <si>
-    <t>Gate Express Car Wash</t>
-  </si>
-  <si>
-    <t>https://gateexpresscarwash.com/</t>
-  </si>
-  <si>
-    <t>Drive &amp; Shine Car Wash</t>
-  </si>
-  <si>
-    <t>Indiana | Michigan</t>
-  </si>
-  <si>
-    <t>https://driveandshine.com/</t>
-  </si>
-  <si>
-    <t>TruShine Car Wash</t>
-  </si>
-  <si>
-    <t>Tennessee | Virginia</t>
-  </si>
-  <si>
-    <t>https://www.trushinecarwash.com/</t>
-  </si>
-  <si>
-    <t>WOW Carwash</t>
-  </si>
-  <si>
-    <t>Garnett Station Partners, LLC</t>
-  </si>
-  <si>
-    <t>https://wowwash.com/</t>
-  </si>
-  <si>
-    <t>Big Peach Car Wash</t>
-  </si>
-  <si>
-    <t>Georgia | Tennessee | Florida</t>
-  </si>
-  <si>
-    <t>https://www.bigpeachusa.com/</t>
-  </si>
-  <si>
-    <t>Buddy Bear Car Wash</t>
-  </si>
-  <si>
-    <t>https://buddybearcarwash.com/</t>
-  </si>
-  <si>
-    <t>Francis &amp; Sons Car Wash</t>
-  </si>
-  <si>
-    <t>Acquired by Raceway Car Wash</t>
-  </si>
-  <si>
-    <t>https://francisandsonscarwash.com/</t>
-  </si>
-  <si>
-    <t>Blue Tide Car Wash</t>
-  </si>
-  <si>
-    <t>South Dakota</t>
-  </si>
-  <si>
-    <t>https://bluetidecarwash.com/</t>
-  </si>
-  <si>
-    <t>Fuller's Car Wash</t>
-  </si>
-  <si>
-    <t>https://fullerscarwash.com/</t>
-  </si>
-  <si>
-    <t>Kaady Car Wash</t>
-  </si>
-  <si>
-    <t>Oregon | Washington | California</t>
-  </si>
-  <si>
-    <t>https://kaady.com/</t>
-  </si>
-  <si>
-    <t>Washman Car Washes</t>
-  </si>
-  <si>
-    <t>https://www.washmanusa.com/</t>
-  </si>
-  <si>
-    <t>Bliss Car Wash</t>
-  </si>
-  <si>
-    <t>https://blisscarwash.com/</t>
-  </si>
-  <si>
-    <t>Fast Eddie's Car Wash &amp; Oil Change</t>
-  </si>
-  <si>
-    <t>https://www.fasteddiescarcare.com/</t>
-  </si>
-  <si>
-    <t>Raindrop Car Wash</t>
-  </si>
-  <si>
-    <t>https://raindropcarwash.com/</t>
-  </si>
-  <si>
-    <t>Rainforest Carwash &amp; Oil Change</t>
-  </si>
-  <si>
-    <t>Louisiana</t>
-  </si>
-  <si>
-    <t>Louisiana | Mississippi</t>
-  </si>
-  <si>
-    <t>https://rainforestclean.com/</t>
-  </si>
-  <si>
-    <t>Zax Auto Wash</t>
-  </si>
-  <si>
-    <t>https://zaxautowash.com/</t>
-  </si>
-  <si>
-    <t>Car Spa</t>
-  </si>
-  <si>
-    <t>Florida | Georgia | Texas | Virginia</t>
-  </si>
-  <si>
-    <t>https://carspa.net/</t>
-  </si>
-  <si>
-    <t>Haffner's</t>
-  </si>
-  <si>
-    <t>Massachusetts | New Hampshire</t>
-  </si>
-  <si>
-    <t>https://haffners.com/</t>
-  </si>
-  <si>
-    <t>Mr. Sparkle Car Wash</t>
-  </si>
-  <si>
-    <t>Connecticut | Massachusetts | New Jersey</t>
-  </si>
-  <si>
-    <t>https://www.mrsparklecarwash.com/</t>
-  </si>
-  <si>
-    <t>Rocky Mountain Car Wash</t>
-  </si>
-  <si>
-    <t>Montana</t>
-  </si>
-  <si>
-    <t>Wyoming | Montana</t>
-  </si>
-  <si>
-    <t>https://rockymountaincarwash.com/</t>
-  </si>
-  <si>
-    <t>Sgt. Clean Car Wash</t>
-  </si>
-  <si>
-    <t>https://sgtclean.com/</t>
-  </si>
-  <si>
-    <t>Shammy Shine Car Washes</t>
-  </si>
-  <si>
-    <t>New Jersey</t>
-  </si>
-  <si>
-    <t>New Jersey | Pennsylvania</t>
-  </si>
-  <si>
-    <t>https://www.shammyshine.com/</t>
-  </si>
-  <si>
-    <t>Cheetah Clean Auto Wash</t>
-  </si>
-  <si>
-    <t>Kentucky | Tennessee</t>
-  </si>
-  <si>
-    <t>https://cheetahclean.com/</t>
-  </si>
-  <si>
     <t>Mach-1 Express Wash</t>
   </si>
   <si>
@@ -1048,13 +1060,13 @@
     <t>https://www.pelicanpointecarwash.com/</t>
   </si>
   <si>
-    <t>Breeze Thru Car Wash</t>
-  </si>
-  <si>
-    <t>Colorado | Wyoming</t>
-  </si>
-  <si>
-    <t>https://breezethrucarwash.com/</t>
+    <t>Xpress Car Wash</t>
+  </si>
+  <si>
+    <t>Louisiana | Texas</t>
+  </si>
+  <si>
+    <t>https://timeitxpresswash.com/</t>
   </si>
   <si>
     <t>Carriage House Car Wash</t>
@@ -1177,12 +1189,6 @@
     <t>https://speedystop.com/</t>
   </si>
   <si>
-    <t>Team Car Wash</t>
-  </si>
-  <si>
-    <t>https://theteamcarwash.com/</t>
-  </si>
-  <si>
     <t>Wash-Rite Express Car Wash</t>
   </si>
   <si>
@@ -1231,6 +1237,12 @@
     <t>https://oceanbluecarwash.com/</t>
   </si>
   <si>
+    <t>Radiant Express Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.radiantexpresscarwash.com/</t>
+  </si>
+  <si>
     <t>Shine Time Super Wash</t>
   </si>
   <si>
@@ -1246,6 +1258,15 @@
     <t>https://supercleanmycar.com/</t>
   </si>
   <si>
+    <t>Wash Factory Car Wash</t>
+  </si>
+  <si>
+    <t>Georgia | Tennessee</t>
+  </si>
+  <si>
+    <t>https://www.washfactorycarwash.com/</t>
+  </si>
+  <si>
     <t>Xtreme Auto Wash</t>
   </si>
   <si>
@@ -1291,12 +1312,6 @@
     <t>https://mrwash.com/</t>
   </si>
   <si>
-    <t>Radiant Express Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.radiantexpresscarwash.com/</t>
-  </si>
-  <si>
     <t>Red Carpet Car Wash</t>
   </si>
   <si>
@@ -1333,15 +1348,6 @@
     <t>https://www.washucarwash.com/</t>
   </si>
   <si>
-    <t>Xpress Car Wash</t>
-  </si>
-  <si>
-    <t>Louisiana | Texas</t>
-  </si>
-  <si>
-    <t>https://timeitxpresswash.com/</t>
-  </si>
-  <si>
     <t>Classy Chassis</t>
   </si>
   <si>
@@ -1357,96 +1363,264 @@
     <t>https://washmycar.ca/</t>
   </si>
   <si>
+    <t>AquaShine Express</t>
+  </si>
+  <si>
+    <t>Georgia | Florida | South Carolina</t>
+  </si>
+  <si>
+    <t>https://aquashineexpress.com/</t>
+  </si>
+  <si>
+    <t>Benny’s Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.bennyscarwash.com/</t>
+  </si>
+  <si>
+    <t>BriteworX Car Washery</t>
+  </si>
+  <si>
+    <t>Missouri | Illinois</t>
+  </si>
+  <si>
+    <t>https://briteworx.com/</t>
+  </si>
+  <si>
+    <t>Cloud 10 Smartwash</t>
+  </si>
+  <si>
+    <t>Pennsylvania | New Jersey</t>
+  </si>
+  <si>
+    <t>https://cloud10smartwash.com/</t>
+  </si>
+  <si>
+    <t>Groove Car Wash</t>
+  </si>
+  <si>
+    <t>Vaquero Ventures</t>
+  </si>
+  <si>
+    <t>Texas | Florida | Oklahoma</t>
+  </si>
+  <si>
+    <t>https://www.groovecarwash.com/</t>
+  </si>
+  <si>
+    <t>Scrubby’s Car Wash</t>
+  </si>
+  <si>
+    <t>South Carolina | North Carolina</t>
+  </si>
+  <si>
+    <t>https://scrubbyscarwashes.com/</t>
+  </si>
+  <si>
+    <t>Skweeky Kleen Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.skweekykleen.com/</t>
+  </si>
+  <si>
+    <t>Speedwash</t>
+  </si>
+  <si>
+    <t>https://www.speedwashes.com/</t>
+  </si>
+  <si>
+    <t>SpeedWash Car Wash</t>
+  </si>
+  <si>
+    <t>Kentucky | Indiana</t>
+  </si>
+  <si>
+    <t>https://speedwashusa.com/</t>
+  </si>
+  <si>
+    <t>WashGuys Car Wash</t>
+  </si>
+  <si>
+    <t>https://washguystx.com/</t>
+  </si>
+  <si>
+    <t>Bubbles Car Washes and Detail Centres</t>
+  </si>
+  <si>
+    <t>Alberta</t>
+  </si>
+  <si>
+    <t>https://bubbles.ca/</t>
+  </si>
+  <si>
+    <t>Sparkle Express Car Wash</t>
+  </si>
+  <si>
+    <t>https://sparklestatus.com/</t>
+  </si>
+  <si>
+    <t>Auto Spa Car Wash (WA)</t>
+  </si>
+  <si>
+    <t>https://www.autospacw.com</t>
+  </si>
+  <si>
     <t>Blue Penguin Car Wash</t>
   </si>
   <si>
     <t>https://www.bluepenguincarwash.com/</t>
   </si>
   <si>
-    <t>BriteworX Car Washery</t>
-  </si>
-  <si>
-    <t>Missouri | Illinois</t>
-  </si>
-  <si>
-    <t>https://briteworx.com/</t>
-  </si>
-  <si>
-    <t>Cloud 10 Smartwash</t>
-  </si>
-  <si>
-    <t>Pennsylvania | New Jersey</t>
-  </si>
-  <si>
-    <t>https://cloud10smartwash.com/</t>
-  </si>
-  <si>
-    <t>Groove Car Wash</t>
-  </si>
-  <si>
-    <t>Vaquero Ventures</t>
-  </si>
-  <si>
-    <t>Texas | Florida | Oklahoma</t>
-  </si>
-  <si>
-    <t>https://www.groovecarwash.com/</t>
-  </si>
-  <si>
-    <t>Scrubby’s Car Wash</t>
-  </si>
-  <si>
-    <t>South Carolina | North Carolina</t>
-  </si>
-  <si>
-    <t>https://scrubbyscarwashes.com/</t>
-  </si>
-  <si>
-    <t>Skweeky Kleen Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.skweekykleen.com/</t>
-  </si>
-  <si>
-    <t>SpeedWash Car Wash</t>
-  </si>
-  <si>
-    <t>Kentucky | Indiana</t>
-  </si>
-  <si>
-    <t>https://speedwashusa.com/</t>
-  </si>
-  <si>
-    <t>WashGuys Car Wash</t>
-  </si>
-  <si>
-    <t>https://washguystx.com/</t>
-  </si>
-  <si>
-    <t>Sparkle Express Car Wash</t>
-  </si>
-  <si>
-    <t>https://sparklestatus.com/</t>
-  </si>
-  <si>
-    <t>Auto Spa Car Wash (WA)</t>
-  </si>
-  <si>
-    <t>https://www.autospacw.com</t>
-  </si>
-  <si>
-    <t>Benny’s Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.bennyscarwash.com/</t>
-  </si>
-  <si>
     <t>Driven Car Wash</t>
   </si>
   <si>
     <t>https://drivencarwash.com/</t>
   </si>
   <si>
+    <t>Jet Splash Car Wash</t>
+  </si>
+  <si>
+    <t>https://jetsplash.com</t>
+  </si>
+  <si>
+    <t>Rocket Wash</t>
+  </si>
+  <si>
+    <t>North Carolina | South Carolina</t>
+  </si>
+  <si>
+    <t>https://rocketcarwashexpress.com/</t>
+  </si>
+  <si>
+    <t>Velocity Car Wash</t>
+  </si>
+  <si>
+    <t>Colorado | Utah</t>
+  </si>
+  <si>
+    <t>https://www.velocitywash.com/</t>
+  </si>
+  <si>
+    <t>Genie Car Wash</t>
+  </si>
+  <si>
+    <t>California | Arizona</t>
+  </si>
+  <si>
+    <t>https://www.geniecarwash.com/</t>
+  </si>
+  <si>
+    <t>American Pride Xpress Carwash</t>
+  </si>
+  <si>
+    <t>https://americanpridexpress.com/</t>
+  </si>
+  <si>
+    <t>Auto Spa LA</t>
+  </si>
+  <si>
+    <t>https://autospala.com/</t>
+  </si>
+  <si>
+    <t>Cadillac Express Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.cadillacexpresscarwash.com/</t>
+  </si>
+  <si>
+    <t>Mr. Splash Car Wash</t>
+  </si>
+  <si>
+    <t>Argosy Private Equity</t>
+  </si>
+  <si>
+    <t>https://mrsplashcarwash.com/</t>
+  </si>
+  <si>
+    <t>Pony Express Carwash</t>
+  </si>
+  <si>
+    <t>https://ponycarwash.com/</t>
+  </si>
+  <si>
+    <t>Snap Clean Car Wash</t>
+  </si>
+  <si>
+    <t>https://snapcleancarwash.com/</t>
+  </si>
+  <si>
+    <t>TipTop Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.tiptopcarwashes.com/</t>
+  </si>
+  <si>
+    <t>Ocean Express Car Wash</t>
+  </si>
+  <si>
+    <t>https://oceancarwashtx.com/</t>
+  </si>
+  <si>
+    <t>Mint Smartwash</t>
+  </si>
+  <si>
+    <t>https://mintsmartwash.com/</t>
+  </si>
+  <si>
+    <t>Halo Car Wash</t>
+  </si>
+  <si>
+    <t>https://halowash.com/</t>
+  </si>
+  <si>
+    <t>Clearwave Car Wash</t>
+  </si>
+  <si>
+    <t>Illinois | Michigan</t>
+  </si>
+  <si>
+    <t>https://clearwavecarwash.com/</t>
+  </si>
+  <si>
+    <t>H2Go Car Wash</t>
+  </si>
+  <si>
+    <t>Privately Owned</t>
+  </si>
+  <si>
+    <t>https://h2gocarwash.com/</t>
+  </si>
+  <si>
+    <t>Supershine Xpress Carwash</t>
+  </si>
+  <si>
+    <t>https://supershinexpress.com/</t>
+  </si>
+  <si>
+    <t>Washtopia Car Wash</t>
+  </si>
+  <si>
+    <t>https://washtopia.com/</t>
+  </si>
+  <si>
+    <t>The Wave Car Wash (WA)</t>
+  </si>
+  <si>
+    <t>https://www.thewavewash.com/</t>
+  </si>
+  <si>
+    <t>Bebo's Carwash</t>
+  </si>
+  <si>
+    <t>https://www.beboscarwash.com/</t>
+  </si>
+  <si>
+    <t>Endless Clean Car Wash</t>
+  </si>
+  <si>
+    <t>https://endlesscleancarwash.com/</t>
+  </si>
+  <si>
     <t>Fabulous Freddy’s Car Wash</t>
   </si>
   <si>
@@ -1456,111 +1630,6 @@
     <t>https://fabfred.com/</t>
   </si>
   <si>
-    <t>Jet Splash Car Wash</t>
-  </si>
-  <si>
-    <t>https://jetsplash.com</t>
-  </si>
-  <si>
-    <t>Rocket Wash</t>
-  </si>
-  <si>
-    <t>North Carolina | South Carolina</t>
-  </si>
-  <si>
-    <t>https://rocketcarwashexpress.com/</t>
-  </si>
-  <si>
-    <t>Velocity Car Wash</t>
-  </si>
-  <si>
-    <t>Colorado | Utah</t>
-  </si>
-  <si>
-    <t>https://www.velocitywash.com/</t>
-  </si>
-  <si>
-    <t>Genie Car Wash</t>
-  </si>
-  <si>
-    <t>California | Arizona</t>
-  </si>
-  <si>
-    <t>https://www.geniecarwash.com/</t>
-  </si>
-  <si>
-    <t>American Pride Xpress Carwash</t>
-  </si>
-  <si>
-    <t>https://americanpridexpress.com/</t>
-  </si>
-  <si>
-    <t>Auto Spa LA</t>
-  </si>
-  <si>
-    <t>https://autospala.com/</t>
-  </si>
-  <si>
-    <t>Pony Express Carwash</t>
-  </si>
-  <si>
-    <t>https://ponycarwash.com/</t>
-  </si>
-  <si>
-    <t>Snap Clean Car Wash</t>
-  </si>
-  <si>
-    <t>https://snapcleancarwash.com/</t>
-  </si>
-  <si>
-    <t>Speedwash</t>
-  </si>
-  <si>
-    <t>https://www.speedwashes.com/</t>
-  </si>
-  <si>
-    <t>TipTop Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.tiptopcarwashes.com/</t>
-  </si>
-  <si>
-    <t>Ocean Express Car Wash</t>
-  </si>
-  <si>
-    <t>https://oceancarwashtx.com/</t>
-  </si>
-  <si>
-    <t>Mint Smartwash</t>
-  </si>
-  <si>
-    <t>Alberta</t>
-  </si>
-  <si>
-    <t>https://mintsmartwash.com/</t>
-  </si>
-  <si>
-    <t>Halo Car Wash</t>
-  </si>
-  <si>
-    <t>https://halowash.com/</t>
-  </si>
-  <si>
-    <t>Cadillac Express Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.cadillacexpresscarwash.com/</t>
-  </si>
-  <si>
-    <t>Clearwave Car Wash</t>
-  </si>
-  <si>
-    <t>Illinois | Michigan</t>
-  </si>
-  <si>
-    <t>https://clearwavecarwash.com/</t>
-  </si>
-  <si>
     <t>Greenhill Car Wash</t>
   </si>
   <si>
@@ -1570,52 +1639,10 @@
     <t>https://greenhillcarwash.com/</t>
   </si>
   <si>
-    <t>H2Go Car Wash</t>
-  </si>
-  <si>
-    <t>Privately Owned</t>
-  </si>
-  <si>
-    <t>https://h2gocarwash.com/</t>
-  </si>
-  <si>
-    <t>Supershine Xpress Carwash</t>
-  </si>
-  <si>
-    <t>https://supershinexpress.com/</t>
-  </si>
-  <si>
-    <t>Washtopia Car Wash</t>
-  </si>
-  <si>
-    <t>https://washtopia.com/</t>
-  </si>
-  <si>
-    <t>The Wave Car Wash (WA)</t>
-  </si>
-  <si>
-    <t>https://www.thewavewash.com/</t>
-  </si>
-  <si>
-    <t>Bebo's Carwash</t>
-  </si>
-  <si>
-    <t>https://www.beboscarwash.com/</t>
-  </si>
-  <si>
-    <t>Endless Clean Car Wash</t>
-  </si>
-  <si>
-    <t>https://endlesscleancarwash.com/</t>
-  </si>
-  <si>
-    <t>Mr. Splash Car Wash</t>
-  </si>
-  <si>
-    <t>Argosy Private Equity</t>
-  </si>
-  <si>
-    <t>https://mrsplashcarwash.com/</t>
+    <t>Magic Brush Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.magicbrushexpress.com/</t>
   </si>
   <si>
     <t>RaceWash</t>
@@ -1675,12 +1702,6 @@
     <t>https://www.gleauxcarwash.com/</t>
   </si>
   <si>
-    <t>Magic Brush Car Wash</t>
-  </si>
-  <si>
-    <t>https://www.magicbrushexpress.com/</t>
-  </si>
-  <si>
     <t>Ridi Stores</t>
   </si>
   <si>
@@ -1702,15 +1723,6 @@
     <t>https://soapynoble.com/</t>
   </si>
   <si>
-    <t>Wash Factory Car Wash</t>
-  </si>
-  <si>
-    <t>Georgia | Tennessee</t>
-  </si>
-  <si>
-    <t>https://www.washfactorycarwash.com/</t>
-  </si>
-  <si>
     <t>Waves Express Car Wash</t>
   </si>
   <si>
@@ -1727,6 +1739,12 @@
   </si>
   <si>
     <t>https://www.mintexpresscarwash.com/</t>
+  </si>
+  <si>
+    <t>Sunshine Car Wash</t>
+  </si>
+  <si>
+    <t>https://www.sunshinewashes.com/</t>
   </si>
   <si>
     <t>Ace Auto Washes</t>
@@ -2155,7 +2173,7 @@
         <v>2004.0</v>
       </c>
       <c r="E4" s="2">
-        <v>350.0</v>
+        <v>365.0</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>21</v>
@@ -2199,7 +2217,7 @@
         <v>1999.0</v>
       </c>
       <c r="E5" s="2">
-        <v>308.0</v>
+        <v>332.0</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>26</v>
@@ -2507,7 +2525,7 @@
         <v>2019.0</v>
       </c>
       <c r="E12" s="2">
-        <v>154.0</v>
+        <v>164.0</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>59</v>
@@ -2727,7 +2745,7 @@
         <v>2022.0</v>
       </c>
       <c r="E17" s="2">
-        <v>95.0</v>
+        <v>100.0</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>82</v>
@@ -2985,22 +3003,22 @@
         <v>9</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="D23" s="2">
         <v>1981.0</v>
       </c>
       <c r="E23" s="2">
-        <v>77.0</v>
+        <v>80.0</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -3023,28 +3041,28 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="D24" s="2">
-        <v>2016.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E24" s="2">
-        <v>65.0</v>
+        <v>77.0</v>
       </c>
       <c r="F24" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -3067,28 +3085,28 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="2">
+        <v>2016.0</v>
+      </c>
+      <c r="E25" s="2">
+        <v>65.0</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="D25" s="2">
-        <v>2007.0</v>
-      </c>
-      <c r="E25" s="2">
-        <v>60.0</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -3111,28 +3129,28 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="D26" s="2">
-        <v>1953.0</v>
+        <v>1948.0</v>
       </c>
       <c r="E26" s="2">
-        <v>59.0</v>
+        <v>63.0</v>
       </c>
       <c r="F26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -3155,28 +3173,28 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" s="2">
+        <v>2007.0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>60.0</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="D27" s="2">
-        <v>1970.0</v>
-      </c>
-      <c r="E27" s="2">
-        <v>58.0</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -3199,28 +3217,28 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="D28" s="2">
-        <v>2015.0</v>
+        <v>1953.0</v>
       </c>
       <c r="E28" s="2">
-        <v>55.0</v>
+        <v>59.0</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -3243,28 +3261,28 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>25</v>
+        <v>128</v>
       </c>
       <c r="D29" s="2">
-        <v>2020.0</v>
+        <v>1970.0</v>
       </c>
       <c r="E29" s="2">
-        <v>54.0</v>
+        <v>58.0</v>
       </c>
       <c r="F29" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="H29" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -3287,28 +3305,28 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>134</v>
+        <v>63</v>
       </c>
       <c r="D30" s="2">
-        <v>1948.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E30" s="2">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -3331,26 +3349,28 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="2">
+        <v>2020.0</v>
+      </c>
+      <c r="E31" s="2">
+        <v>54.0</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="D31" s="2">
-        <v>1981.0</v>
-      </c>
-      <c r="E31" s="2">
-        <v>51.0</v>
-      </c>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -3373,28 +3393,26 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D32" s="2">
-        <v>1957.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E32" s="2">
         <v>51.0</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F32" s="1"/>
       <c r="G32" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -3417,28 +3435,28 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>10</v>
+        <v>143</v>
       </c>
       <c r="D33" s="2">
-        <v>2012.0</v>
+        <v>1957.0</v>
       </c>
       <c r="E33" s="2">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G33" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H33" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
@@ -3461,28 +3479,28 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D34" s="2">
-        <v>1988.0</v>
+        <v>2012.0</v>
       </c>
       <c r="E34" s="2">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="F34" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H34" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
@@ -3505,25 +3523,25 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>122</v>
+        <v>25</v>
       </c>
       <c r="D35" s="2">
-        <v>1997.0</v>
+        <v>1988.0</v>
       </c>
       <c r="E35" s="2">
         <v>49.0</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>36</v>
+        <v>149</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>151</v>
@@ -3555,22 +3573,22 @@
         <v>9</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="D36" s="2">
-        <v>2013.0</v>
+        <v>1997.0</v>
       </c>
       <c r="E36" s="2">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G36" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>154</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -3593,28 +3611,28 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>156</v>
+        <v>72</v>
       </c>
       <c r="D37" s="2">
-        <v>1959.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E37" s="2">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -3637,28 +3655,28 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>15</v>
+        <v>158</v>
       </c>
       <c r="D38" s="2">
-        <v>2009.0</v>
+        <v>1976.0</v>
       </c>
       <c r="E38" s="2">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="F38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
@@ -3681,28 +3699,28 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>68</v>
+        <v>162</v>
       </c>
       <c r="D39" s="2">
-        <v>1948.0</v>
+        <v>1959.0</v>
       </c>
       <c r="E39" s="2">
-        <v>44.0</v>
+        <v>47.0</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G39" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H39" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
@@ -3725,28 +3743,28 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="D40" s="2">
-        <v>1995.0</v>
+        <v>2009.0</v>
       </c>
       <c r="E40" s="2">
-        <v>42.0</v>
+        <v>46.0</v>
       </c>
       <c r="F40" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="H40" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
@@ -3769,28 +3787,28 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>171</v>
+        <v>68</v>
       </c>
       <c r="D41" s="2">
-        <v>1976.0</v>
+        <v>1948.0</v>
       </c>
       <c r="E41" s="2">
-        <v>41.0</v>
+        <v>44.0</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -3813,28 +3831,28 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="D42" s="2">
-        <v>2011.0</v>
+        <v>1995.0</v>
       </c>
       <c r="E42" s="2">
-        <v>36.0</v>
+        <v>42.0</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>36</v>
+        <v>173</v>
       </c>
       <c r="G42" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
@@ -3857,16 +3875,16 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D43" s="2">
-        <v>2018.0</v>
+        <v>2011.0</v>
       </c>
       <c r="E43" s="2">
         <v>36.0</v>
@@ -3875,10 +3893,10 @@
         <v>36</v>
       </c>
       <c r="G43" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>179</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -3901,28 +3919,28 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D44" s="2">
-        <v>2013.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E44" s="2">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="F44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
@@ -3945,28 +3963,28 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="D45" s="2">
-        <v>2012.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E45" s="2">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>36</v>
+        <v>183</v>
       </c>
       <c r="G45" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H45" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>185</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -3989,28 +4007,28 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D46" s="2">
-        <v>1967.0</v>
+        <v>1965.0</v>
       </c>
       <c r="E46" s="2">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
@@ -4033,16 +4051,16 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="D47" s="2">
-        <v>2016.0</v>
+        <v>1967.0</v>
       </c>
       <c r="E47" s="2">
         <v>32.0</v>
@@ -4051,10 +4069,10 @@
         <v>36</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -4077,28 +4095,28 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>72</v>
+        <v>191</v>
       </c>
       <c r="D48" s="2">
-        <v>2018.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E48" s="2">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
@@ -4121,28 +4139,28 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="D49" s="2">
-        <v>2019.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E49" s="2">
         <v>31.0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>197</v>
+        <v>36</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
@@ -4165,13 +4183,13 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D50" s="2">
         <v>2012.0</v>
@@ -4183,10 +4201,10 @@
         <v>36</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
@@ -4209,13 +4227,13 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D51" s="2">
         <v>2015.0</v>
@@ -4224,13 +4242,13 @@
         <v>30.0</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
@@ -4253,7 +4271,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>9</v>
@@ -4274,7 +4292,7 @@
         <v>20</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -4297,7 +4315,7 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>9</v>
@@ -4315,10 +4333,10 @@
         <v>36</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
@@ -4341,16 +4359,16 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>138</v>
+        <v>63</v>
       </c>
       <c r="D54" s="2">
-        <v>1965.0</v>
+        <v>2012.0</v>
       </c>
       <c r="E54" s="2">
         <v>28.0</v>
@@ -4359,10 +4377,10 @@
         <v>36</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>138</v>
+        <v>211</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
@@ -4385,7 +4403,7 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>9</v>
@@ -4400,13 +4418,13 @@
         <v>28.0</v>
       </c>
       <c r="F55" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H55" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -4429,7 +4447,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>9</v>
@@ -4447,10 +4465,10 @@
         <v>36</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -4473,7 +4491,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>9</v>
@@ -4491,10 +4509,10 @@
         <v>36</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -4517,7 +4535,7 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>9</v>
@@ -4532,13 +4550,13 @@
         <v>26.0</v>
       </c>
       <c r="F58" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="H58" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
@@ -4561,13 +4579,13 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D59" s="2">
         <v>2020.0</v>
@@ -4576,13 +4594,13 @@
         <v>26.0</v>
       </c>
       <c r="F59" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H59" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>233</v>
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
@@ -4605,13 +4623,13 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D60" s="2">
         <v>1981.0</v>
@@ -4620,13 +4638,13 @@
         <v>25.0</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G60" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H60" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>237</v>
       </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
@@ -4649,13 +4667,13 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D61" s="2">
         <v>2000.0</v>
@@ -4664,13 +4682,13 @@
         <v>25.0</v>
       </c>
       <c r="F61" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H61" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
@@ -4693,7 +4711,7 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>9</v>
@@ -4708,13 +4726,13 @@
         <v>25.0</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
@@ -4737,23 +4755,29 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C63" s="1"/>
+      <c r="C63" s="1" t="s">
+        <v>140</v>
+      </c>
       <c r="D63" s="2">
-        <v>2021.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E63" s="2">
-        <v>24.0</v>
-      </c>
-      <c r="F63" s="1"/>
+        <v>25.0</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>245</v>
+      </c>
       <c r="G63" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="H63" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="H63" s="1"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -4780,24 +4804,18 @@
       <c r="B64" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="C64" s="1"/>
       <c r="D64" s="2">
-        <v>2013.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E64" s="2">
         <v>24.0</v>
       </c>
-      <c r="F64" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F64" s="1"/>
       <c r="G64" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H64" s="3" t="s">
         <v>249</v>
       </c>
+      <c r="H64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
@@ -4869,7 +4887,7 @@
         <v>9</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D66" s="2">
         <v>2012.0</v>
@@ -5045,10 +5063,10 @@
         <v>9</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="D70" s="2">
-        <v>1951.0</v>
+        <v>1966.0</v>
       </c>
       <c r="E70" s="2">
         <v>23.0</v>
@@ -5089,10 +5107,10 @@
         <v>9</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>122</v>
+        <v>271</v>
       </c>
       <c r="D71" s="2">
-        <v>1966.0</v>
+        <v>2020.0</v>
       </c>
       <c r="E71" s="2">
         <v>23.0</v>
@@ -5133,19 +5151,19 @@
         <v>9</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D72" s="2">
-        <v>2019.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E72" s="2">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>274</v>
@@ -5177,19 +5195,19 @@
         <v>9</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D73" s="2">
-        <v>1981.0</v>
+        <v>1982.0</v>
       </c>
       <c r="E73" s="2">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>276</v>
@@ -5221,10 +5239,10 @@
         <v>9</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>77</v>
+        <v>143</v>
       </c>
       <c r="D74" s="2">
-        <v>2017.0</v>
+        <v>1951.0</v>
       </c>
       <c r="E74" s="2">
         <v>21.0</v>
@@ -5233,10 +5251,10 @@
         <v>36</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>77</v>
+        <v>278</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
@@ -5259,13 +5277,13 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="D75" s="2">
         <v>1997.0</v>
@@ -5277,10 +5295,10 @@
         <v>36</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
@@ -5303,16 +5321,16 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D76" s="2">
-        <v>2019.0</v>
+        <v>2017.0</v>
       </c>
       <c r="E76" s="2">
         <v>20.0</v>
@@ -5321,7 +5339,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>283</v>
+        <v>77</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>284</v>
@@ -5353,19 +5371,19 @@
         <v>9</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>156</v>
+        <v>72</v>
       </c>
       <c r="D77" s="2">
-        <v>2016.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E77" s="2">
         <v>20.0</v>
       </c>
       <c r="F77" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G77" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>287</v>
@@ -5397,19 +5415,19 @@
         <v>9</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>25</v>
+        <v>162</v>
       </c>
       <c r="D78" s="2">
-        <v>2021.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E78" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>36</v>
+        <v>289</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>289</v>
+        <v>162</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>290</v>
@@ -5441,10 +5459,10 @@
         <v>9</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D79" s="2">
-        <v>1982.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E79" s="2">
         <v>19.0</v>
@@ -5453,11 +5471,9 @@
         <v>36</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H79" s="3" t="s">
         <v>292</v>
       </c>
+      <c r="H79" s="1"/>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
@@ -5747,10 +5763,10 @@
         <v>9</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>35</v>
+        <v>228</v>
       </c>
       <c r="D86" s="2">
-        <v>1977.0</v>
+        <v>2007.0</v>
       </c>
       <c r="E86" s="2">
         <v>17.0</v>
@@ -5759,10 +5775,10 @@
         <v>36</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>35</v>
+        <v>309</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
@@ -5785,16 +5801,16 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>171</v>
+        <v>35</v>
       </c>
       <c r="D87" s="2">
-        <v>2017.0</v>
+        <v>1977.0</v>
       </c>
       <c r="E87" s="2">
         <v>17.0</v>
@@ -5803,10 +5819,10 @@
         <v>36</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>171</v>
+        <v>35</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
@@ -5829,16 +5845,16 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>313</v>
+        <v>158</v>
       </c>
       <c r="D88" s="2">
-        <v>1993.0</v>
+        <v>2017.0</v>
       </c>
       <c r="E88" s="2">
         <v>17.0</v>
@@ -5847,10 +5863,10 @@
         <v>36</v>
       </c>
       <c r="G88" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H88" s="3" t="s">
         <v>314</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>315</v>
       </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
@@ -5873,16 +5889,16 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>35</v>
+        <v>316</v>
       </c>
       <c r="D89" s="2">
-        <v>2015.0</v>
+        <v>1993.0</v>
       </c>
       <c r="E89" s="2">
         <v>17.0</v>
@@ -5891,10 +5907,10 @@
         <v>36</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>35</v>
+        <v>317</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
@@ -5917,25 +5933,25 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="D90" s="2">
-        <v>1999.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E90" s="2">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>319</v>
+        <v>35</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>320</v>
@@ -5967,10 +5983,10 @@
         <v>9</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="D91" s="2">
-        <v>1995.0</v>
+        <v>2007.0</v>
       </c>
       <c r="E91" s="2">
         <v>16.0</v>
@@ -6011,10 +6027,10 @@
         <v>9</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="D92" s="2">
-        <v>1966.0</v>
+        <v>1999.0</v>
       </c>
       <c r="E92" s="2">
         <v>16.0</v>
@@ -6055,10 +6071,10 @@
         <v>9</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>328</v>
+        <v>128</v>
       </c>
       <c r="D93" s="2">
-        <v>2001.0</v>
+        <v>1995.0</v>
       </c>
       <c r="E93" s="2">
         <v>16.0</v>
@@ -6067,10 +6083,10 @@
         <v>36</v>
       </c>
       <c r="G93" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="H93" s="3" t="s">
         <v>329</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>330</v>
       </c>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
@@ -6093,16 +6109,16 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="D94" s="2">
-        <v>2013.0</v>
+        <v>1966.0</v>
       </c>
       <c r="E94" s="2">
         <v>16.0</v>
@@ -6111,7 +6127,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>332</v>
@@ -6146,7 +6162,7 @@
         <v>334</v>
       </c>
       <c r="D95" s="2">
-        <v>1976.0</v>
+        <v>2001.0</v>
       </c>
       <c r="E95" s="2">
         <v>16.0</v>
@@ -6187,22 +6203,22 @@
         <v>9</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>230</v>
+        <v>68</v>
       </c>
       <c r="D96" s="2">
-        <v>2007.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E96" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G96" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H96" s="3" t="s">
         <v>338</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>339</v>
       </c>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
@@ -6225,28 +6241,28 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>171</v>
+        <v>271</v>
       </c>
       <c r="D97" s="2">
-        <v>2018.0</v>
+        <v>1976.0</v>
       </c>
       <c r="E97" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G97" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="H97" s="3" t="s">
         <v>341</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>342</v>
       </c>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
@@ -6269,28 +6285,28 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>313</v>
+        <v>63</v>
       </c>
       <c r="D98" s="2">
-        <v>2000.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E98" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>313</v>
+        <v>63</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
@@ -6313,28 +6329,28 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>58</v>
+        <v>158</v>
       </c>
       <c r="D99" s="2">
-        <v>2007.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E99" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G99" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="H99" s="3" t="s">
         <v>346</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>347</v>
       </c>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
@@ -6357,28 +6373,28 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>68</v>
+        <v>316</v>
       </c>
       <c r="D100" s="2">
-        <v>2019.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E100" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>349</v>
+        <v>36</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>350</v>
+        <v>316</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
@@ -6401,28 +6417,26 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D101" s="2">
-        <v>2020.0</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="D101" s="1"/>
       <c r="E101" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
@@ -6445,28 +6459,28 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>356</v>
+        <v>68</v>
       </c>
       <c r="D102" s="2">
-        <v>1969.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E102" s="2">
         <v>14.0</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>36</v>
+        <v>353</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
@@ -6489,16 +6503,16 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>313</v>
+        <v>10</v>
       </c>
       <c r="D103" s="2">
-        <v>2013.0</v>
+        <v>2020.0</v>
       </c>
       <c r="E103" s="2">
         <v>14.0</v>
@@ -6507,10 +6521,10 @@
         <v>36</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
@@ -6533,16 +6547,16 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>114</v>
+        <v>360</v>
       </c>
       <c r="D104" s="2">
-        <v>1987.0</v>
+        <v>1969.0</v>
       </c>
       <c r="E104" s="2">
         <v>14.0</v>
@@ -6551,10 +6565,10 @@
         <v>36</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
@@ -6577,26 +6591,28 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>366</v>
+        <v>316</v>
       </c>
       <c r="D105" s="2">
-        <v>2008.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E105" s="2">
         <v>14.0</v>
       </c>
-      <c r="F105" s="1"/>
+      <c r="F105" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G105" s="1" t="s">
-        <v>63</v>
+        <v>364</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
@@ -6619,16 +6635,16 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>334</v>
+        <v>120</v>
       </c>
       <c r="D106" s="2">
-        <v>1994.0</v>
+        <v>1987.0</v>
       </c>
       <c r="E106" s="2">
         <v>14.0</v>
@@ -6637,10 +6653,10 @@
         <v>36</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
@@ -6663,28 +6679,26 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C107" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D107" s="2">
+        <v>2008.0</v>
+      </c>
+      <c r="E107" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="F107" s="1"/>
+      <c r="G107" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D107" s="2">
-        <v>1997.0</v>
-      </c>
-      <c r="E107" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>373</v>
-      </c>
       <c r="H107" s="3" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
@@ -6707,28 +6721,28 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>77</v>
+        <v>271</v>
       </c>
       <c r="D108" s="2">
-        <v>2020.0</v>
+        <v>1994.0</v>
       </c>
       <c r="E108" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>376</v>
+        <v>36</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>77</v>
+        <v>373</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
@@ -6751,28 +6765,28 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>379</v>
+        <v>63</v>
       </c>
       <c r="D109" s="2">
-        <v>1981.0</v>
+        <v>1997.0</v>
       </c>
       <c r="E109" s="2">
         <v>13.0</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>36</v>
+        <v>376</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
@@ -6795,26 +6809,28 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>383</v>
+        <v>77</v>
       </c>
       <c r="D110" s="2">
-        <v>2013.0</v>
+        <v>2020.0</v>
       </c>
       <c r="E110" s="2">
         <v>13.0</v>
       </c>
-      <c r="F110" s="1"/>
+      <c r="F110" s="1" t="s">
+        <v>380</v>
+      </c>
       <c r="G110" s="1" t="s">
-        <v>384</v>
+        <v>77</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
@@ -6837,16 +6853,16 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>63</v>
+        <v>383</v>
       </c>
       <c r="D111" s="2">
-        <v>1983.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E111" s="2">
         <v>13.0</v>
@@ -6855,10 +6871,10 @@
         <v>36</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>63</v>
+        <v>384</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
@@ -6881,25 +6897,23 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>334</v>
+        <v>387</v>
       </c>
       <c r="D112" s="2">
-        <v>2020.0</v>
+        <v>2013.0</v>
       </c>
       <c r="E112" s="2">
         <v>13.0</v>
       </c>
-      <c r="F112" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F112" s="1"/>
       <c r="G112" s="1" t="s">
-        <v>334</v>
+        <v>388</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>389</v>
@@ -6931,22 +6945,22 @@
         <v>9</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="D113" s="2">
-        <v>2021.0</v>
+        <v>1983.0</v>
       </c>
       <c r="E113" s="2">
         <v>13.0</v>
       </c>
       <c r="F113" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H113" s="3" t="s">
         <v>391</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>393</v>
       </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
@@ -6969,28 +6983,28 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>235</v>
+        <v>25</v>
       </c>
       <c r="D114" s="2">
-        <v>2010.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E114" s="2">
         <v>13.0</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>36</v>
+        <v>393</v>
       </c>
       <c r="G114" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="H114" s="3" t="s">
         <v>395</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>396</v>
       </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -7013,28 +7027,28 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>44</v>
+        <v>233</v>
       </c>
       <c r="D115" s="2">
-        <v>2023.0</v>
+        <v>2010.0</v>
       </c>
       <c r="E115" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="F115" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="H115" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H115" s="3" t="s">
-        <v>399</v>
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -7057,25 +7071,25 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D116" s="2">
-        <v>2017.0</v>
+        <v>2023.0</v>
       </c>
       <c r="E116" s="2">
         <v>12.0</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>36</v>
+        <v>400</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="H116" s="3" t="s">
         <v>401</v>
@@ -7107,10 +7121,10 @@
         <v>9</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D117" s="2">
-        <v>1980.0</v>
+        <v>2017.0</v>
       </c>
       <c r="E117" s="2">
         <v>12.0</v>
@@ -7119,7 +7133,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>403</v>
@@ -7154,7 +7168,7 @@
         <v>15</v>
       </c>
       <c r="D118" s="2">
-        <v>2004.0</v>
+        <v>1980.0</v>
       </c>
       <c r="E118" s="2">
         <v>12.0</v>
@@ -7195,10 +7209,10 @@
         <v>9</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>171</v>
+        <v>15</v>
       </c>
       <c r="D119" s="2">
-        <v>2007.0</v>
+        <v>2004.0</v>
       </c>
       <c r="E119" s="2">
         <v>12.0</v>
@@ -7207,10 +7221,10 @@
         <v>36</v>
       </c>
       <c r="G119" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H119" s="3" t="s">
         <v>407</v>
-      </c>
-      <c r="H119" s="3" t="s">
-        <v>408</v>
       </c>
       <c r="I119" s="1"/>
       <c r="J119" s="1"/>
@@ -7233,16 +7247,16 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="D120" s="2">
-        <v>1990.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E120" s="2">
         <v>12.0</v>
@@ -7251,10 +7265,10 @@
         <v>36</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I120" s="1"/>
       <c r="J120" s="1"/>
@@ -7277,16 +7291,16 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>383</v>
+        <v>158</v>
       </c>
       <c r="D121" s="2">
-        <v>2006.0</v>
+        <v>2007.0</v>
       </c>
       <c r="E121" s="2">
         <v>12.0</v>
@@ -7295,9 +7309,11 @@
         <v>36</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H121" s="1"/>
+        <v>411</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>412</v>
+      </c>
       <c r="I121" s="1"/>
       <c r="J121" s="1"/>
       <c r="K121" s="1"/>
@@ -7319,7 +7335,7 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>9</v>
@@ -7328,10 +7344,10 @@
         <v>20</v>
       </c>
       <c r="D122" s="2">
-        <v>1964.0</v>
+        <v>1990.0</v>
       </c>
       <c r="E122" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>36</v>
@@ -7340,7 +7356,7 @@
         <v>20</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I122" s="1"/>
       <c r="J122" s="1"/>
@@ -7363,28 +7379,28 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D123" s="2">
-        <v>1993.0</v>
+        <v>2011.0</v>
       </c>
       <c r="E123" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>20</v>
+        <v>416</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="I123" s="1"/>
       <c r="J123" s="1"/>
@@ -7407,29 +7423,27 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>44</v>
+        <v>387</v>
       </c>
       <c r="D124" s="2">
-        <v>2019.0</v>
+        <v>2006.0</v>
       </c>
       <c r="E124" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H124" s="3" t="s">
-        <v>417</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="H124" s="1"/>
       <c r="I124" s="1"/>
       <c r="J124" s="1"/>
       <c r="K124" s="1"/>
@@ -7451,16 +7465,16 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>235</v>
+        <v>20</v>
       </c>
       <c r="D125" s="2">
-        <v>2023.0</v>
+        <v>1964.0</v>
       </c>
       <c r="E125" s="2">
         <v>11.0</v>
@@ -7469,7 +7483,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>419</v>
+        <v>20</v>
       </c>
       <c r="H125" s="3" t="s">
         <v>420</v>
@@ -7501,10 +7515,10 @@
         <v>9</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D126" s="2">
-        <v>2015.0</v>
+        <v>1993.0</v>
       </c>
       <c r="E126" s="2">
         <v>11.0</v>
@@ -7513,7 +7527,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="H126" s="3" t="s">
         <v>422</v>
@@ -7545,10 +7559,10 @@
         <v>9</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>235</v>
+        <v>44</v>
       </c>
       <c r="D127" s="2">
-        <v>1958.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E127" s="2">
         <v>11.0</v>
@@ -7557,10 +7571,10 @@
         <v>36</v>
       </c>
       <c r="G127" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H127" s="3" t="s">
         <v>424</v>
-      </c>
-      <c r="H127" s="3" t="s">
-        <v>425</v>
       </c>
       <c r="I127" s="1"/>
       <c r="J127" s="1"/>
@@ -7583,16 +7597,16 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="D128" s="2">
-        <v>2019.0</v>
+        <v>2023.0</v>
       </c>
       <c r="E128" s="2">
         <v>11.0</v>
@@ -7601,7 +7615,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>77</v>
+        <v>426</v>
       </c>
       <c r="H128" s="3" t="s">
         <v>427</v>
@@ -7633,10 +7647,10 @@
         <v>9</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="D129" s="2">
-        <v>1950.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E129" s="2">
         <v>11.0</v>
@@ -7645,7 +7659,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="H129" s="3" t="s">
         <v>429</v>
@@ -7677,10 +7691,10 @@
         <v>9</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>72</v>
+        <v>233</v>
       </c>
       <c r="D130" s="2">
-        <v>2018.0</v>
+        <v>1958.0</v>
       </c>
       <c r="E130" s="2">
         <v>11.0</v>
@@ -7721,10 +7735,10 @@
         <v>9</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>434</v>
+        <v>20</v>
       </c>
       <c r="D131" s="2">
-        <v>1947.0</v>
+        <v>1950.0</v>
       </c>
       <c r="E131" s="2">
         <v>11.0</v>
@@ -7733,10 +7747,10 @@
         <v>36</v>
       </c>
       <c r="G131" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H131" s="3" t="s">
         <v>434</v>
-      </c>
-      <c r="H131" s="3" t="s">
-        <v>435</v>
       </c>
       <c r="I131" s="1"/>
       <c r="J131" s="1"/>
@@ -7759,28 +7773,28 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D132" s="2">
-        <v>2019.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E132" s="2">
         <v>11.0</v>
       </c>
       <c r="F132" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="H132" s="3" t="s">
         <v>437</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="H132" s="3" t="s">
-        <v>439</v>
       </c>
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
@@ -7803,15 +7817,17 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="D133" s="1"/>
+        <v>439</v>
+      </c>
+      <c r="D133" s="2">
+        <v>1947.0</v>
+      </c>
       <c r="E133" s="2">
         <v>11.0</v>
       </c>
@@ -7819,10 +7835,10 @@
         <v>36</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
@@ -7845,23 +7861,25 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="D134" s="2">
-        <v>1985.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E134" s="2">
         <v>11.0</v>
       </c>
-      <c r="F134" s="1"/>
+      <c r="F134" s="1" t="s">
+        <v>442</v>
+      </c>
       <c r="G134" s="1" t="s">
-        <v>141</v>
+        <v>443</v>
       </c>
       <c r="H134" s="3" t="s">
         <v>444</v>
@@ -7893,18 +7911,20 @@
         <v>9</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>446</v>
+        <v>143</v>
       </c>
       <c r="D135" s="2">
-        <v>1991.0</v>
+        <v>1985.0</v>
       </c>
       <c r="E135" s="2">
         <v>11.0</v>
       </c>
       <c r="F135" s="1"/>
-      <c r="G135" s="1"/>
+      <c r="G135" s="1" t="s">
+        <v>143</v>
+      </c>
       <c r="H135" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
@@ -7927,26 +7947,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>25</v>
+        <v>448</v>
       </c>
       <c r="D136" s="2">
-        <v>2022.0</v>
+        <v>1991.0</v>
       </c>
       <c r="E136" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>148</v>
-      </c>
+        <v>11.0</v>
+      </c>
+      <c r="F136" s="1"/>
+      <c r="G136" s="1"/>
       <c r="H136" s="3" t="s">
         <v>449</v>
       </c>
@@ -7977,17 +7993,15 @@
         <v>9</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D137" s="2">
-        <v>2016.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E137" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>11.0</v>
+      </c>
+      <c r="F137" s="1"/>
       <c r="G137" s="1" t="s">
         <v>451</v>
       </c>
@@ -8021,10 +8035,10 @@
         <v>9</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>105</v>
+        <v>316</v>
       </c>
       <c r="D138" s="2">
-        <v>2018.0</v>
+        <v>1951.0</v>
       </c>
       <c r="E138" s="2">
         <v>10.0</v>
@@ -8033,10 +8047,10 @@
         <v>36</v>
       </c>
       <c r="G138" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="H138" s="3" t="s">
         <v>454</v>
-      </c>
-      <c r="H138" s="3" t="s">
-        <v>455</v>
       </c>
       <c r="I138" s="1"/>
       <c r="J138" s="1"/>
@@ -8059,28 +8073,28 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="D139" s="2">
-        <v>2022.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E139" s="2">
         <v>10.0</v>
       </c>
       <c r="F139" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="H139" s="3" t="s">
         <v>457</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="H139" s="3" t="s">
-        <v>459</v>
       </c>
       <c r="I139" s="1"/>
       <c r="J139" s="1"/>
@@ -8103,16 +8117,16 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>204</v>
+        <v>107</v>
       </c>
       <c r="D140" s="2">
-        <v>2015.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E140" s="2">
         <v>10.0</v>
@@ -8121,10 +8135,10 @@
         <v>36</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="I140" s="1"/>
       <c r="J140" s="1"/>
@@ -8147,25 +8161,25 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="D141" s="2">
-        <v>2005.0</v>
+        <v>2022.0</v>
       </c>
       <c r="E141" s="2">
         <v>10.0</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>36</v>
+        <v>462</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>25</v>
+        <v>463</v>
       </c>
       <c r="H141" s="3" t="s">
         <v>464</v>
@@ -8197,10 +8211,10 @@
         <v>9</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="D142" s="2">
-        <v>1999.0</v>
+        <v>2015.0</v>
       </c>
       <c r="E142" s="2">
         <v>10.0</v>
@@ -8241,10 +8255,10 @@
         <v>9</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="D143" s="2">
-        <v>2009.0</v>
+        <v>2005.0</v>
       </c>
       <c r="E143" s="2">
         <v>10.0</v>
@@ -8253,7 +8267,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="H143" s="3" t="s">
         <v>469</v>
@@ -8285,17 +8299,19 @@
         <v>9</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="D144" s="2">
-        <v>2009.0</v>
+        <v>2014.0</v>
       </c>
       <c r="E144" s="2">
         <v>10.0</v>
       </c>
-      <c r="F144" s="1"/>
+      <c r="F144" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G144" s="1" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="H144" s="3" t="s">
         <v>471</v>
@@ -8327,22 +8343,22 @@
         <v>9</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>141</v>
+        <v>228</v>
       </c>
       <c r="D145" s="2">
-        <v>2002.0</v>
+        <v>1999.0</v>
       </c>
       <c r="E145" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>141</v>
+        <v>473</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I145" s="1"/>
       <c r="J145" s="1"/>
@@ -8365,28 +8381,28 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>313</v>
+        <v>63</v>
       </c>
       <c r="D146" s="2">
-        <v>1951.0</v>
+        <v>2009.0</v>
       </c>
       <c r="E146" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>313</v>
+        <v>63</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I146" s="1"/>
       <c r="J146" s="1"/>
@@ -8409,28 +8425,24 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>44</v>
+        <v>478</v>
       </c>
       <c r="D147" s="2">
-        <v>2021.0</v>
+        <v>1983.0</v>
       </c>
       <c r="E147" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G147" s="1" t="s">
-        <v>44</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F147" s="1"/>
+      <c r="G147" s="1"/>
       <c r="H147" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I147" s="1"/>
       <c r="J147" s="1"/>
@@ -8453,28 +8465,26 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>156</v>
+        <v>44</v>
       </c>
       <c r="D148" s="2">
-        <v>1998.0</v>
+        <v>2009.0</v>
       </c>
       <c r="E148" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F148" s="1"/>
       <c r="G148" s="1" t="s">
-        <v>479</v>
+        <v>44</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I148" s="1"/>
       <c r="J148" s="1"/>
@@ -8497,16 +8507,16 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>239</v>
+        <v>143</v>
       </c>
       <c r="D149" s="2">
-        <v>2003.0</v>
+        <v>2002.0</v>
       </c>
       <c r="E149" s="2">
         <v>9.0</v>
@@ -8515,10 +8525,10 @@
         <v>36</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>239</v>
+        <v>143</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="I149" s="1"/>
       <c r="J149" s="1"/>
@@ -8541,23 +8551,25 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D150" s="2">
-        <v>2021.0</v>
+        <v>2022.0</v>
       </c>
       <c r="E150" s="2">
         <v>9.0</v>
       </c>
-      <c r="F150" s="1"/>
+      <c r="F150" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G150" s="1" t="s">
-        <v>484</v>
+        <v>150</v>
       </c>
       <c r="H150" s="3" t="s">
         <v>485</v>
@@ -8589,7 +8601,7 @@
         <v>9</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="D151" s="2">
         <v>2021.0</v>
@@ -8601,10 +8613,10 @@
         <v>36</v>
       </c>
       <c r="G151" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H151" s="3" t="s">
         <v>487</v>
-      </c>
-      <c r="H151" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="I151" s="1"/>
       <c r="J151" s="1"/>
@@ -8627,26 +8639,28 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="D152" s="2">
-        <v>1982.0</v>
+        <v>2003.0</v>
       </c>
       <c r="E152" s="2">
         <v>9.0</v>
       </c>
-      <c r="F152" s="1"/>
+      <c r="F152" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G152" s="1" t="s">
-        <v>490</v>
+        <v>237</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I152" s="1"/>
       <c r="J152" s="1"/>
@@ -8669,7 +8683,7 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>9</v>
@@ -8678,19 +8692,17 @@
         <v>10</v>
       </c>
       <c r="D153" s="2">
-        <v>1981.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E153" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>9.0</v>
+      </c>
+      <c r="F153" s="1"/>
       <c r="G153" s="1" t="s">
-        <v>10</v>
+        <v>491</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="I153" s="1"/>
       <c r="J153" s="1"/>
@@ -8713,25 +8725,25 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>313</v>
+        <v>58</v>
       </c>
       <c r="D154" s="2">
-        <v>1998.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E154" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>313</v>
+        <v>494</v>
       </c>
       <c r="H154" s="3" t="s">
         <v>495</v>
@@ -8763,22 +8775,20 @@
         <v>9</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>356</v>
+        <v>20</v>
       </c>
       <c r="D155" s="2">
-        <v>2018.0</v>
+        <v>1982.0</v>
       </c>
       <c r="E155" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>9.0</v>
+      </c>
+      <c r="F155" s="1"/>
       <c r="G155" s="1" t="s">
-        <v>356</v>
+        <v>497</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I155" s="1"/>
       <c r="J155" s="1"/>
@@ -8801,16 +8811,16 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="D156" s="2">
-        <v>2017.0</v>
+        <v>1981.0</v>
       </c>
       <c r="E156" s="2">
         <v>8.0</v>
@@ -8819,10 +8829,10 @@
         <v>36</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I156" s="1"/>
       <c r="J156" s="1"/>
@@ -8845,16 +8855,16 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>20</v>
+        <v>316</v>
       </c>
       <c r="D157" s="2">
-        <v>2014.0</v>
+        <v>1998.0</v>
       </c>
       <c r="E157" s="2">
         <v>8.0</v>
@@ -8863,10 +8873,10 @@
         <v>36</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>20</v>
+        <v>316</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="I157" s="1"/>
       <c r="J157" s="1"/>
@@ -8889,26 +8899,28 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>134</v>
+        <v>63</v>
       </c>
       <c r="D158" s="2">
-        <v>2024.0</v>
+        <v>2012.0</v>
       </c>
       <c r="E158" s="2">
         <v>8.0</v>
       </c>
-      <c r="F158" s="1"/>
+      <c r="F158" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G158" s="1" t="s">
-        <v>134</v>
+        <v>63</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I158" s="1"/>
       <c r="J158" s="1"/>
@@ -8931,26 +8943,28 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>63</v>
+        <v>439</v>
       </c>
       <c r="D159" s="2">
-        <v>2011.0</v>
+        <v>2010.0</v>
       </c>
       <c r="E159" s="2">
         <v>8.0</v>
       </c>
-      <c r="F159" s="1"/>
+      <c r="F159" s="1" t="s">
+        <v>506</v>
+      </c>
       <c r="G159" s="1" t="s">
-        <v>63</v>
+        <v>439</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="I159" s="1"/>
       <c r="J159" s="1"/>
@@ -8973,26 +8987,28 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>507</v>
+        <v>360</v>
       </c>
       <c r="D160" s="2">
-        <v>2014.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E160" s="2">
         <v>8.0</v>
       </c>
-      <c r="F160" s="1"/>
+      <c r="F160" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G160" s="1" t="s">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="I160" s="1"/>
       <c r="J160" s="1"/>
@@ -9015,24 +9031,28 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>446</v>
+        <v>63</v>
       </c>
       <c r="D161" s="2">
-        <v>2019.0</v>
+        <v>2017.0</v>
       </c>
       <c r="E161" s="2">
         <v>8.0</v>
       </c>
-      <c r="F161" s="1"/>
-      <c r="G161" s="1"/>
+      <c r="F161" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="H161" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I161" s="1"/>
       <c r="J161" s="1"/>
@@ -9055,28 +9075,26 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D162" s="2">
-        <v>2012.0</v>
+        <v>2024.0</v>
       </c>
       <c r="E162" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>8.0</v>
+      </c>
+      <c r="F162" s="1"/>
       <c r="G162" s="1" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="I162" s="1"/>
       <c r="J162" s="1"/>
@@ -9099,25 +9117,23 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D163" s="2">
-        <v>2016.0</v>
+        <v>2011.0</v>
       </c>
       <c r="E163" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="F163" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>8.0</v>
+      </c>
+      <c r="F163" s="1"/>
       <c r="G163" s="1" t="s">
-        <v>514</v>
+        <v>63</v>
       </c>
       <c r="H163" s="3" t="s">
         <v>515</v>
@@ -9149,20 +9165,20 @@
         <v>9</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>517</v>
+        <v>478</v>
       </c>
       <c r="D164" s="2">
-        <v>2009.0</v>
+        <v>2014.0</v>
       </c>
       <c r="E164" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="F164" s="1"/>
       <c r="G164" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="H164" s="3" t="s">
         <v>517</v>
-      </c>
-      <c r="H164" s="3" t="s">
-        <v>518</v>
       </c>
       <c r="I164" s="1"/>
       <c r="J164" s="1"/>
@@ -9185,28 +9201,24 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>20</v>
+        <v>448</v>
       </c>
       <c r="D165" s="2">
-        <v>2010.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E165" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="F165" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>8.0</v>
+      </c>
+      <c r="F165" s="1"/>
+      <c r="G165" s="1"/>
       <c r="H165" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="I165" s="1"/>
       <c r="J165" s="1"/>
@@ -9229,16 +9241,16 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D166" s="2">
-        <v>2019.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E166" s="2">
         <v>7.0</v>
@@ -9247,10 +9259,10 @@
         <v>36</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>25</v>
+        <v>521</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="I166" s="1"/>
       <c r="J166" s="1"/>
@@ -9273,25 +9285,25 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="D167" s="2">
-        <v>2016.0</v>
+        <v>2010.0</v>
       </c>
       <c r="E167" s="2">
         <v>7.0</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>36</v>
+        <v>524</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="H167" s="3" t="s">
         <v>525</v>
@@ -9323,17 +9335,19 @@
         <v>9</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="D168" s="2">
-        <v>2005.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E168" s="2">
         <v>7.0</v>
       </c>
-      <c r="F168" s="1"/>
+      <c r="F168" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G168" s="1" t="s">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="H168" s="3" t="s">
         <v>527</v>
@@ -9365,17 +9379,19 @@
         <v>9</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="D169" s="2">
-        <v>1964.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E169" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="F169" s="1"/>
+        <v>7.0</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G169" s="1" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="H169" s="3" t="s">
         <v>529</v>
@@ -9407,19 +9423,17 @@
         <v>9</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="D170" s="2">
-        <v>2018.0</v>
+        <v>2005.0</v>
       </c>
       <c r="E170" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="F170" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>7.0</v>
+      </c>
+      <c r="F170" s="1"/>
       <c r="G170" s="1" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="H170" s="3" t="s">
         <v>531</v>
@@ -9451,22 +9465,20 @@
         <v>9</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>434</v>
+        <v>158</v>
       </c>
       <c r="D171" s="2">
-        <v>2010.0</v>
+        <v>1964.0</v>
       </c>
       <c r="E171" s="2">
         <v>6.0</v>
       </c>
-      <c r="F171" s="1" t="s">
+      <c r="F171" s="1"/>
+      <c r="G171" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H171" s="3" t="s">
         <v>533</v>
-      </c>
-      <c r="G171" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="H171" s="3" t="s">
-        <v>534</v>
       </c>
       <c r="I171" s="1"/>
       <c r="J171" s="1"/>
@@ -9489,16 +9501,16 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="D172" s="2">
-        <v>2010.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E172" s="2">
         <v>6.0</v>
@@ -9507,10 +9519,10 @@
         <v>36</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>536</v>
+        <v>63</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="I172" s="1"/>
       <c r="J172" s="1"/>
@@ -9533,16 +9545,16 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="D173" s="2">
-        <v>1985.0</v>
+        <v>1998.0</v>
       </c>
       <c r="E173" s="2">
         <v>6.0</v>
@@ -9551,10 +9563,10 @@
         <v>36</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>141</v>
+        <v>537</v>
       </c>
       <c r="H173" s="3" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I173" s="1"/>
       <c r="J173" s="1"/>
@@ -9577,22 +9589,24 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>507</v>
+        <v>540</v>
       </c>
       <c r="D174" s="2">
-        <v>2019.0</v>
+        <v>2009.0</v>
       </c>
       <c r="E174" s="2">
         <v>6.0</v>
       </c>
       <c r="F174" s="1"/>
-      <c r="G174" s="1"/>
+      <c r="G174" s="1" t="s">
+        <v>540</v>
+      </c>
       <c r="H174" s="3" t="s">
         <v>541</v>
       </c>
@@ -9623,22 +9637,22 @@
         <v>9</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>543</v>
+        <v>20</v>
       </c>
       <c r="D175" s="2">
-        <v>2006.0</v>
+        <v>2021.0</v>
       </c>
       <c r="E175" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G175" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H175" s="3" t="s">
         <v>543</v>
-      </c>
-      <c r="H175" s="3" t="s">
-        <v>544</v>
       </c>
       <c r="I175" s="1"/>
       <c r="J175" s="1"/>
@@ -9661,23 +9675,25 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D176" s="2">
-        <v>2016.0</v>
+        <v>2010.0</v>
       </c>
       <c r="E176" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="F176" s="1"/>
+        <v>6.0</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G176" s="1" t="s">
-        <v>72</v>
+        <v>545</v>
       </c>
       <c r="H176" s="3" t="s">
         <v>546</v>
@@ -9709,19 +9725,19 @@
         <v>9</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>230</v>
+        <v>143</v>
       </c>
       <c r="D177" s="2">
-        <v>2018.0</v>
+        <v>1985.0</v>
       </c>
       <c r="E177" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>230</v>
+        <v>143</v>
       </c>
       <c r="H177" s="3" t="s">
         <v>548</v>
@@ -9753,22 +9769,18 @@
         <v>9</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>58</v>
+        <v>478</v>
       </c>
       <c r="D178" s="2">
-        <v>1978.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E178" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="F178" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G178" s="1" t="s">
+        <v>6.0</v>
+      </c>
+      <c r="F178" s="1"/>
+      <c r="G178" s="1"/>
+      <c r="H178" s="3" t="s">
         <v>550</v>
-      </c>
-      <c r="H178" s="3" t="s">
-        <v>551</v>
       </c>
       <c r="I178" s="1"/>
       <c r="J178" s="1"/>
@@ -9791,23 +9803,25 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>63</v>
+        <v>552</v>
       </c>
       <c r="D179" s="2">
-        <v>2019.0</v>
+        <v>2006.0</v>
       </c>
       <c r="E179" s="2">
         <v>5.0</v>
       </c>
-      <c r="F179" s="1"/>
+      <c r="F179" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G179" s="1" t="s">
-        <v>63</v>
+        <v>552</v>
       </c>
       <c r="H179" s="3" t="s">
         <v>553</v>
@@ -9839,19 +9853,17 @@
         <v>9</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="D180" s="2">
-        <v>2021.0</v>
+        <v>2016.0</v>
       </c>
       <c r="E180" s="2">
         <v>5.0</v>
       </c>
-      <c r="F180" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F180" s="1"/>
       <c r="G180" s="1" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="H180" s="3" t="s">
         <v>555</v>
@@ -9883,10 +9895,10 @@
         <v>9</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>68</v>
+        <v>228</v>
       </c>
       <c r="D181" s="2">
-        <v>2002.0</v>
+        <v>2018.0</v>
       </c>
       <c r="E181" s="2">
         <v>5.0</v>
@@ -9895,7 +9907,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>68</v>
+        <v>228</v>
       </c>
       <c r="H181" s="3" t="s">
         <v>557</v>
@@ -9927,10 +9939,10 @@
         <v>9</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="D182" s="2">
-        <v>2023.0</v>
+        <v>1978.0</v>
       </c>
       <c r="E182" s="2">
         <v>5.0</v>
@@ -9939,10 +9951,10 @@
         <v>36</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>72</v>
+        <v>559</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="I182" s="1"/>
       <c r="J182" s="1"/>
@@ -9965,25 +9977,23 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="D183" s="2">
-        <v>2022.0</v>
+        <v>2019.0</v>
       </c>
       <c r="E183" s="2">
         <v>5.0</v>
       </c>
-      <c r="F183" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F183" s="1"/>
       <c r="G183" s="1" t="s">
-        <v>561</v>
+        <v>63</v>
       </c>
       <c r="H183" s="3" t="s">
         <v>562</v>
@@ -10015,10 +10025,10 @@
         <v>9</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="D184" s="2">
-        <v>2011.0</v>
+        <v>2002.0</v>
       </c>
       <c r="E184" s="2">
         <v>5.0</v>
@@ -10027,10 +10037,10 @@
         <v>36</v>
       </c>
       <c r="G184" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H184" s="3" t="s">
         <v>564</v>
-      </c>
-      <c r="H184" s="3" t="s">
-        <v>565</v>
       </c>
       <c r="I184" s="1"/>
       <c r="J184" s="1"/>
@@ -10053,16 +10063,16 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>204</v>
+        <v>72</v>
       </c>
       <c r="D185" s="2">
-        <v>2017.0</v>
+        <v>2023.0</v>
       </c>
       <c r="E185" s="2">
         <v>5.0</v>
@@ -10071,10 +10081,10 @@
         <v>36</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>204</v>
+        <v>72</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="I185" s="1"/>
       <c r="J185" s="1"/>
@@ -10097,23 +10107,25 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="D186" s="2">
-        <v>2009.0</v>
+        <v>2022.0</v>
       </c>
       <c r="E186" s="2">
         <v>5.0</v>
       </c>
-      <c r="F186" s="1"/>
+      <c r="F186" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G186" s="1" t="s">
-        <v>63</v>
+        <v>568</v>
       </c>
       <c r="H186" s="3" t="s">
         <v>569</v>
@@ -10145,17 +10157,19 @@
         <v>9</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>63</v>
+        <v>201</v>
       </c>
       <c r="D187" s="2">
-        <v>2018.0</v>
+        <v>2017.0</v>
       </c>
       <c r="E187" s="2">
         <v>5.0</v>
       </c>
-      <c r="F187" s="1"/>
+      <c r="F187" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G187" s="1" t="s">
-        <v>63</v>
+        <v>201</v>
       </c>
       <c r="H187" s="3" t="s">
         <v>571</v>
@@ -10186,16 +10200,22 @@
       <c r="B188" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C188" s="1"/>
-      <c r="D188" s="1"/>
+      <c r="C188" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D188" s="2">
+        <v>2009.0</v>
+      </c>
       <c r="E188" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="F188" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G188" s="1"/>
-      <c r="H188" s="1"/>
+        <v>5.0</v>
+      </c>
+      <c r="F188" s="1"/>
+      <c r="G188" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H188" s="3" t="s">
+        <v>573</v>
+      </c>
       <c r="I188" s="1"/>
       <c r="J188" s="1"/>
       <c r="K188" s="1"/>
@@ -10217,28 +10237,26 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="D189" s="2">
         <v>2018.0</v>
       </c>
       <c r="E189" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="F189" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F189" s="1"/>
       <c r="G189" s="1" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="H189" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="I189" s="1"/>
       <c r="J189" s="1"/>
@@ -10260,14 +10278,28 @@
       <c r="Z189" s="1"/>
     </row>
     <row r="190">
-      <c r="A190" s="1"/>
-      <c r="B190" s="1"/>
-      <c r="C190" s="1"/>
-      <c r="D190" s="1"/>
-      <c r="E190" s="1"/>
+      <c r="A190" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D190" s="2">
+        <v>2019.0</v>
+      </c>
+      <c r="E190" s="2">
+        <v>5.0</v>
+      </c>
       <c r="F190" s="1"/>
-      <c r="G190" s="1"/>
-      <c r="H190" s="1"/>
+      <c r="G190" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H190" s="3" t="s">
+        <v>577</v>
+      </c>
       <c r="I190" s="1"/>
       <c r="J190" s="1"/>
       <c r="K190" s="1"/>
@@ -10288,12 +10320,20 @@
       <c r="Z190" s="1"/>
     </row>
     <row r="191">
-      <c r="A191" s="1"/>
-      <c r="B191" s="1"/>
+      <c r="A191" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="C191" s="1"/>
       <c r="D191" s="1"/>
-      <c r="E191" s="1"/>
-      <c r="F191" s="1"/>
+      <c r="E191" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G191" s="1"/>
       <c r="H191" s="1"/>
       <c r="I191" s="1"/>
@@ -10316,14 +10356,30 @@
       <c r="Z191" s="1"/>
     </row>
     <row r="192">
-      <c r="A192" s="1"/>
-      <c r="B192" s="1"/>
-      <c r="C192" s="1"/>
-      <c r="D192" s="1"/>
-      <c r="E192" s="1"/>
-      <c r="F192" s="1"/>
-      <c r="G192" s="1"/>
-      <c r="H192" s="1"/>
+      <c r="A192" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D192" s="2">
+        <v>2018.0</v>
+      </c>
+      <c r="E192" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H192" s="3" t="s">
+        <v>580</v>
+      </c>
       <c r="I192" s="1"/>
       <c r="J192" s="1"/>
       <c r="K192" s="1"/>
@@ -33031,7 +33087,7 @@
     <hyperlink r:id="rId60" ref="H60"/>
     <hyperlink r:id="rId61" ref="H61"/>
     <hyperlink r:id="rId62" ref="H62"/>
-    <hyperlink r:id="rId63" ref="H64"/>
+    <hyperlink r:id="rId63" ref="H63"/>
     <hyperlink r:id="rId64" ref="H65"/>
     <hyperlink r:id="rId65" ref="H66"/>
     <hyperlink r:id="rId66" ref="H67"/>
@@ -33046,116 +33102,118 @@
     <hyperlink r:id="rId75" ref="H76"/>
     <hyperlink r:id="rId76" ref="H77"/>
     <hyperlink r:id="rId77" ref="H78"/>
-    <hyperlink r:id="rId78" ref="H79"/>
-    <hyperlink r:id="rId79" ref="H80"/>
-    <hyperlink r:id="rId80" ref="H81"/>
-    <hyperlink r:id="rId81" ref="H82"/>
-    <hyperlink r:id="rId82" ref="H83"/>
-    <hyperlink r:id="rId83" ref="H84"/>
-    <hyperlink r:id="rId84" ref="H85"/>
-    <hyperlink r:id="rId85" ref="H86"/>
-    <hyperlink r:id="rId86" ref="H87"/>
-    <hyperlink r:id="rId87" ref="H88"/>
-    <hyperlink r:id="rId88" ref="H89"/>
-    <hyperlink r:id="rId89" ref="H90"/>
-    <hyperlink r:id="rId90" ref="H91"/>
-    <hyperlink r:id="rId91" ref="H92"/>
-    <hyperlink r:id="rId92" ref="H93"/>
-    <hyperlink r:id="rId93" ref="H94"/>
-    <hyperlink r:id="rId94" ref="H95"/>
-    <hyperlink r:id="rId95" ref="H96"/>
-    <hyperlink r:id="rId96" ref="H97"/>
-    <hyperlink r:id="rId97" ref="H98"/>
-    <hyperlink r:id="rId98" ref="H99"/>
-    <hyperlink r:id="rId99" ref="H100"/>
-    <hyperlink r:id="rId100" ref="H101"/>
-    <hyperlink r:id="rId101" ref="H102"/>
-    <hyperlink r:id="rId102" ref="H103"/>
-    <hyperlink r:id="rId103" ref="H104"/>
-    <hyperlink r:id="rId104" ref="H105"/>
-    <hyperlink r:id="rId105" ref="H106"/>
-    <hyperlink r:id="rId106" ref="H107"/>
-    <hyperlink r:id="rId107" ref="H108"/>
-    <hyperlink r:id="rId108" ref="H109"/>
-    <hyperlink r:id="rId109" ref="H110"/>
-    <hyperlink r:id="rId110" ref="H111"/>
-    <hyperlink r:id="rId111" ref="H112"/>
-    <hyperlink r:id="rId112" ref="H113"/>
-    <hyperlink r:id="rId113" ref="H114"/>
-    <hyperlink r:id="rId114" ref="H115"/>
-    <hyperlink r:id="rId115" ref="H116"/>
-    <hyperlink r:id="rId116" ref="H117"/>
-    <hyperlink r:id="rId117" ref="H118"/>
-    <hyperlink r:id="rId118" ref="H119"/>
-    <hyperlink r:id="rId119" ref="H120"/>
+    <hyperlink r:id="rId78" ref="H80"/>
+    <hyperlink r:id="rId79" ref="H81"/>
+    <hyperlink r:id="rId80" ref="H82"/>
+    <hyperlink r:id="rId81" ref="H83"/>
+    <hyperlink r:id="rId82" ref="H84"/>
+    <hyperlink r:id="rId83" ref="H85"/>
+    <hyperlink r:id="rId84" ref="H86"/>
+    <hyperlink r:id="rId85" ref="H87"/>
+    <hyperlink r:id="rId86" ref="H88"/>
+    <hyperlink r:id="rId87" ref="H89"/>
+    <hyperlink r:id="rId88" ref="H90"/>
+    <hyperlink r:id="rId89" ref="H91"/>
+    <hyperlink r:id="rId90" ref="H92"/>
+    <hyperlink r:id="rId91" ref="H93"/>
+    <hyperlink r:id="rId92" ref="H94"/>
+    <hyperlink r:id="rId93" ref="H95"/>
+    <hyperlink r:id="rId94" ref="H96"/>
+    <hyperlink r:id="rId95" ref="H97"/>
+    <hyperlink r:id="rId96" ref="H98"/>
+    <hyperlink r:id="rId97" ref="H99"/>
+    <hyperlink r:id="rId98" ref="H100"/>
+    <hyperlink r:id="rId99" ref="H101"/>
+    <hyperlink r:id="rId100" ref="H102"/>
+    <hyperlink r:id="rId101" ref="H103"/>
+    <hyperlink r:id="rId102" ref="H104"/>
+    <hyperlink r:id="rId103" ref="H105"/>
+    <hyperlink r:id="rId104" ref="H106"/>
+    <hyperlink r:id="rId105" ref="H107"/>
+    <hyperlink r:id="rId106" ref="H108"/>
+    <hyperlink r:id="rId107" ref="H109"/>
+    <hyperlink r:id="rId108" ref="H110"/>
+    <hyperlink r:id="rId109" ref="H111"/>
+    <hyperlink r:id="rId110" ref="H112"/>
+    <hyperlink r:id="rId111" ref="H113"/>
+    <hyperlink r:id="rId112" ref="H114"/>
+    <hyperlink r:id="rId113" ref="H115"/>
+    <hyperlink r:id="rId114" ref="H116"/>
+    <hyperlink r:id="rId115" ref="H117"/>
+    <hyperlink r:id="rId116" ref="H118"/>
+    <hyperlink r:id="rId117" ref="H119"/>
+    <hyperlink r:id="rId118" ref="H120"/>
+    <hyperlink r:id="rId119" ref="H121"/>
     <hyperlink r:id="rId120" ref="H122"/>
     <hyperlink r:id="rId121" ref="H123"/>
-    <hyperlink r:id="rId122" ref="H124"/>
-    <hyperlink r:id="rId123" ref="H125"/>
-    <hyperlink r:id="rId124" ref="H126"/>
-    <hyperlink r:id="rId125" ref="H127"/>
-    <hyperlink r:id="rId126" ref="H128"/>
-    <hyperlink r:id="rId127" ref="H129"/>
-    <hyperlink r:id="rId128" ref="H130"/>
-    <hyperlink r:id="rId129" ref="H131"/>
-    <hyperlink r:id="rId130" ref="H132"/>
-    <hyperlink r:id="rId131" ref="H133"/>
-    <hyperlink r:id="rId132" ref="H134"/>
-    <hyperlink r:id="rId133" ref="H135"/>
-    <hyperlink r:id="rId134" ref="H136"/>
-    <hyperlink r:id="rId135" ref="H137"/>
-    <hyperlink r:id="rId136" ref="H138"/>
-    <hyperlink r:id="rId137" ref="H139"/>
-    <hyperlink r:id="rId138" ref="H140"/>
-    <hyperlink r:id="rId139" ref="H141"/>
-    <hyperlink r:id="rId140" ref="H142"/>
-    <hyperlink r:id="rId141" ref="H143"/>
-    <hyperlink r:id="rId142" ref="H144"/>
-    <hyperlink r:id="rId143" ref="H145"/>
-    <hyperlink r:id="rId144" ref="H146"/>
-    <hyperlink r:id="rId145" ref="H147"/>
-    <hyperlink r:id="rId146" ref="H148"/>
-    <hyperlink r:id="rId147" ref="H149"/>
-    <hyperlink r:id="rId148" ref="H150"/>
-    <hyperlink r:id="rId149" ref="H151"/>
-    <hyperlink r:id="rId150" ref="H152"/>
-    <hyperlink r:id="rId151" ref="H153"/>
-    <hyperlink r:id="rId152" ref="H154"/>
-    <hyperlink r:id="rId153" ref="H155"/>
-    <hyperlink r:id="rId154" ref="H156"/>
-    <hyperlink r:id="rId155" ref="H157"/>
-    <hyperlink r:id="rId156" ref="H158"/>
-    <hyperlink r:id="rId157" ref="H159"/>
-    <hyperlink r:id="rId158" ref="H160"/>
-    <hyperlink r:id="rId159" ref="H161"/>
-    <hyperlink r:id="rId160" ref="H162"/>
-    <hyperlink r:id="rId161" ref="H163"/>
-    <hyperlink r:id="rId162" ref="H164"/>
-    <hyperlink r:id="rId163" ref="H165"/>
-    <hyperlink r:id="rId164" ref="H166"/>
-    <hyperlink r:id="rId165" ref="H167"/>
-    <hyperlink r:id="rId166" ref="H168"/>
-    <hyperlink r:id="rId167" ref="H169"/>
-    <hyperlink r:id="rId168" ref="H170"/>
-    <hyperlink r:id="rId169" ref="H171"/>
-    <hyperlink r:id="rId170" ref="H172"/>
-    <hyperlink r:id="rId171" ref="H173"/>
-    <hyperlink r:id="rId172" ref="H174"/>
-    <hyperlink r:id="rId173" ref="H175"/>
-    <hyperlink r:id="rId174" ref="H176"/>
-    <hyperlink r:id="rId175" ref="H177"/>
-    <hyperlink r:id="rId176" ref="H178"/>
-    <hyperlink r:id="rId177" ref="H179"/>
-    <hyperlink r:id="rId178" ref="H180"/>
-    <hyperlink r:id="rId179" ref="H181"/>
-    <hyperlink r:id="rId180" ref="H182"/>
-    <hyperlink r:id="rId181" ref="H183"/>
-    <hyperlink r:id="rId182" ref="H184"/>
-    <hyperlink r:id="rId183" ref="H185"/>
-    <hyperlink r:id="rId184" ref="H186"/>
-    <hyperlink r:id="rId185" ref="H187"/>
+    <hyperlink r:id="rId122" ref="H125"/>
+    <hyperlink r:id="rId123" ref="H126"/>
+    <hyperlink r:id="rId124" ref="H127"/>
+    <hyperlink r:id="rId125" ref="H128"/>
+    <hyperlink r:id="rId126" ref="H129"/>
+    <hyperlink r:id="rId127" ref="H130"/>
+    <hyperlink r:id="rId128" ref="H131"/>
+    <hyperlink r:id="rId129" ref="H132"/>
+    <hyperlink r:id="rId130" ref="H133"/>
+    <hyperlink r:id="rId131" ref="H134"/>
+    <hyperlink r:id="rId132" ref="H135"/>
+    <hyperlink r:id="rId133" ref="H136"/>
+    <hyperlink r:id="rId134" ref="H137"/>
+    <hyperlink r:id="rId135" ref="H138"/>
+    <hyperlink r:id="rId136" ref="H139"/>
+    <hyperlink r:id="rId137" ref="H140"/>
+    <hyperlink r:id="rId138" ref="H141"/>
+    <hyperlink r:id="rId139" ref="H142"/>
+    <hyperlink r:id="rId140" ref="H143"/>
+    <hyperlink r:id="rId141" ref="H144"/>
+    <hyperlink r:id="rId142" ref="H145"/>
+    <hyperlink r:id="rId143" ref="H146"/>
+    <hyperlink r:id="rId144" ref="H147"/>
+    <hyperlink r:id="rId145" ref="H148"/>
+    <hyperlink r:id="rId146" ref="H149"/>
+    <hyperlink r:id="rId147" ref="H150"/>
+    <hyperlink r:id="rId148" ref="H151"/>
+    <hyperlink r:id="rId149" ref="H152"/>
+    <hyperlink r:id="rId150" ref="H153"/>
+    <hyperlink r:id="rId151" ref="H154"/>
+    <hyperlink r:id="rId152" ref="H155"/>
+    <hyperlink r:id="rId153" ref="H156"/>
+    <hyperlink r:id="rId154" ref="H157"/>
+    <hyperlink r:id="rId155" ref="H158"/>
+    <hyperlink r:id="rId156" ref="H159"/>
+    <hyperlink r:id="rId157" ref="H160"/>
+    <hyperlink r:id="rId158" ref="H161"/>
+    <hyperlink r:id="rId159" ref="H162"/>
+    <hyperlink r:id="rId160" ref="H163"/>
+    <hyperlink r:id="rId161" ref="H164"/>
+    <hyperlink r:id="rId162" ref="H165"/>
+    <hyperlink r:id="rId163" ref="H166"/>
+    <hyperlink r:id="rId164" ref="H167"/>
+    <hyperlink r:id="rId165" ref="H168"/>
+    <hyperlink r:id="rId166" ref="H169"/>
+    <hyperlink r:id="rId167" ref="H170"/>
+    <hyperlink r:id="rId168" ref="H171"/>
+    <hyperlink r:id="rId169" ref="H172"/>
+    <hyperlink r:id="rId170" ref="H173"/>
+    <hyperlink r:id="rId171" ref="H174"/>
+    <hyperlink r:id="rId172" ref="H175"/>
+    <hyperlink r:id="rId173" ref="H176"/>
+    <hyperlink r:id="rId174" ref="H177"/>
+    <hyperlink r:id="rId175" ref="H178"/>
+    <hyperlink r:id="rId176" ref="H179"/>
+    <hyperlink r:id="rId177" ref="H180"/>
+    <hyperlink r:id="rId178" ref="H181"/>
+    <hyperlink r:id="rId179" ref="H182"/>
+    <hyperlink r:id="rId180" ref="H183"/>
+    <hyperlink r:id="rId181" ref="H184"/>
+    <hyperlink r:id="rId182" ref="H185"/>
+    <hyperlink r:id="rId183" ref="H186"/>
+    <hyperlink r:id="rId184" ref="H187"/>
+    <hyperlink r:id="rId185" ref="H188"/>
     <hyperlink r:id="rId186" ref="H189"/>
+    <hyperlink r:id="rId187" ref="H190"/>
+    <hyperlink r:id="rId188" ref="H192"/>
   </hyperlinks>
-  <drawing r:id="rId187"/>
+  <drawing r:id="rId189"/>
 </worksheet>
 </file>